--- a/data/vessels/2026-10-11.xlsx
+++ b/data/vessels/2026-10-11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="415143" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92EB8BE5-BEB8-4CD0-940C-8D6940542A3F}"/>
+  <xr:revisionPtr revIDLastSave="416027" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{245621A7-B2E6-4FD6-90A2-3EAC3EFB2EF5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="239">
   <si>
     <t>Harbor</t>
   </si>
@@ -272,6 +272,18 @@
     <t>158A</t>
   </si>
   <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM BYBLOS</t>
+  </si>
+  <si>
+    <t>CPN00/CPN01</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
     <t>TOTE</t>
   </si>
   <si>
@@ -290,18 +302,6 @@
     <t>Multipurpose</t>
   </si>
   <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM BYBLOS</t>
-  </si>
-  <si>
-    <t>CPN00/CPN01</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
     <t>LIBERTY PRIDE</t>
   </si>
   <si>
@@ -380,7 +380,7 @@
     <t>NORTH STAR</t>
   </si>
   <si>
-    <t>Waiting 3.4 days</t>
+    <t>Waiting 3.7 days</t>
   </si>
   <si>
     <t>WC4/TP5</t>
@@ -395,27 +395,27 @@
     <t>Maersk</t>
   </si>
   <si>
+    <t>XIN YING KOU</t>
+  </si>
+  <si>
+    <t>269N/269S</t>
+  </si>
+  <si>
     <t>CMA CGM ALMAVIVA</t>
   </si>
   <si>
     <t>CPN02/CPN03</t>
   </si>
   <si>
-    <t>XIN YING KOU</t>
-  </si>
-  <si>
-    <t>269N/269S</t>
+    <t>SALVIA ACE</t>
+  </si>
+  <si>
+    <t>177A</t>
   </si>
   <si>
     <t>MODERN LINK</t>
   </si>
   <si>
-    <t>SALVIA ACE</t>
-  </si>
-  <si>
-    <t>177A</t>
-  </si>
-  <si>
     <t>THEMISA</t>
   </si>
   <si>
@@ -425,12 +425,12 @@
     <t>Wallenius</t>
   </si>
   <si>
+    <t>SM QINGDAO</t>
+  </si>
+  <si>
     <t>ONE OWL</t>
   </si>
   <si>
-    <t>SM QINGDAO</t>
-  </si>
-  <si>
     <t>PCT</t>
   </si>
   <si>
@@ -473,15 +473,15 @@
     <t>643S</t>
   </si>
   <si>
+    <t>THEMIS LEADER</t>
+  </si>
+  <si>
     <t>ARC ENDEAVOR</t>
   </si>
   <si>
     <t>A6180</t>
   </si>
   <si>
-    <t>THEMIS LEADER</t>
-  </si>
-  <si>
     <t>VIENNA EXPRESS</t>
   </si>
   <si>
@@ -521,13 +521,19 @@
     <t>159E</t>
   </si>
   <si>
+    <t>CARNATION ACE</t>
+  </si>
+  <si>
+    <t>107A</t>
+  </si>
+  <si>
     <t>POLARIS MILA</t>
   </si>
   <si>
-    <t>CARNATION ACE</t>
-  </si>
-  <si>
-    <t>107A</t>
+    <t>OOCL SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>199E</t>
   </si>
   <si>
     <t>MAUNAWILI</t>
@@ -536,27 +542,21 @@
     <t>642S</t>
   </si>
   <si>
-    <t>OOCL SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>199E</t>
-  </si>
-  <si>
     <t>RJ PFEIFFER</t>
   </si>
   <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
     <t>ARC HONOR</t>
   </si>
   <si>
     <t>ED616</t>
   </si>
   <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
     <t>EVER SALUTE</t>
   </si>
   <si>
@@ -746,28 +746,16 @@
     <t>102N</t>
   </si>
   <si>
+    <t>GLOVIS LEGEND</t>
+  </si>
+  <si>
     <t>GLOVIS TREASURE</t>
   </si>
   <si>
-    <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
     <t>ONE FANTASTIC</t>
   </si>
   <si>
     <t>FANT0011E</t>
-  </si>
-  <si>
-    <t>EVER MOST</t>
-  </si>
-  <si>
-    <t>1474-011E</t>
-  </si>
-  <si>
-    <t>LOTUS A</t>
-  </si>
-  <si>
-    <t>CPN080S19</t>
   </si>
 </sst>
 </file>
@@ -840,10 +828,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L127" totalsRowShown="0">
-  <autoFilter ref="A1:L127" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L127">
-    <sortCondition ref="J2:J127"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L118" totalsRowShown="0">
+  <autoFilter ref="A1:L118" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L118">
+    <sortCondition ref="J2:J118"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1180,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L127"/>
+  <dimension ref="A1:L118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1409,34 +1397,37 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
         <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
       </c>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J7" s="2">
-        <v>46305.208333333336</v>
+        <v>46306.25</v>
       </c>
       <c r="K7" s="2">
-        <v>46308.166666666664</v>
+        <v>46306.583333333336</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
@@ -1444,40 +1435,37 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J8" s="2">
         <v>46306.25</v>
       </c>
       <c r="K8" s="2">
-        <v>46306.583333333336</v>
+        <v>46307.166666666664</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1485,31 +1473,31 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="2">
-        <v>46306.25</v>
+        <v>46306.291666666664</v>
       </c>
       <c r="K9" s="2">
-        <v>46307.166666666664</v>
+        <v>46308.166666666664</v>
       </c>
       <c r="L9" t="s">
         <v>43</v>
@@ -1517,37 +1505,40 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
       </c>
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J10" s="2">
-        <v>46306.291666666664</v>
+        <v>46306.541666666664</v>
       </c>
       <c r="K10" s="2">
-        <v>46308.166666666664</v>
+        <v>46306.999305555553</v>
       </c>
       <c r="L10" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1555,19 +1546,19 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s">
         <v>17</v>
@@ -1579,10 +1570,10 @@
         <v>25</v>
       </c>
       <c r="J11" s="2">
-        <v>46306.541666666664</v>
+        <v>46306.625</v>
       </c>
       <c r="K11" s="2">
-        <v>46306.999305555553</v>
+        <v>46307.166666666664</v>
       </c>
       <c r="L11" t="s">
         <v>26</v>
@@ -1593,57 +1584,51 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
         <v>17</v>
       </c>
-      <c r="H12" t="s">
-        <v>36</v>
-      </c>
       <c r="I12" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J12" s="2">
         <v>46306.625</v>
       </c>
       <c r="K12" s="2">
-        <v>46307.166666666664</v>
+        <v>46308.75</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="G13" t="s">
         <v>17</v>
@@ -1652,10 +1637,10 @@
         <v>18</v>
       </c>
       <c r="J13" s="2">
-        <v>46306.625</v>
+        <v>46307.25</v>
       </c>
       <c r="K13" s="2">
-        <v>46308.75</v>
+        <v>46307.75</v>
       </c>
       <c r="L13" t="s">
         <v>43</v>
@@ -1666,16 +1651,19 @@
         <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="G14" t="s">
         <v>17</v>
@@ -1684,10 +1672,10 @@
         <v>18</v>
       </c>
       <c r="J14" s="2">
-        <v>46307.25</v>
+        <v>46308.291666666664</v>
       </c>
       <c r="K14" s="2">
-        <v>46307.75</v>
+        <v>46309.75</v>
       </c>
       <c r="L14" t="s">
         <v>43</v>
@@ -1701,13 +1689,13 @@
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F15" t="s">
         <v>31</v>
@@ -1722,7 +1710,7 @@
         <v>46308.291666666664</v>
       </c>
       <c r="K15" s="2">
-        <v>46309.75</v>
+        <v>46310.166666666664</v>
       </c>
       <c r="L15" t="s">
         <v>43</v>
@@ -1730,34 +1718,37 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>66</v>
+      </c>
+      <c r="H16" t="s">
+        <v>67</v>
       </c>
       <c r="I16" t="s">
         <v>18</v>
       </c>
       <c r="J16" s="2">
-        <v>46308.291666666664</v>
+        <v>46309.104166666664</v>
       </c>
       <c r="K16" s="2">
-        <v>46310.166666666664</v>
+        <v>46309.916666666664</v>
       </c>
       <c r="L16" t="s">
         <v>43</v>
@@ -1768,34 +1759,31 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
         <v>18</v>
       </c>
       <c r="J17" s="2">
-        <v>46309.104166666664</v>
+        <v>46309.208333333336</v>
       </c>
       <c r="K17" s="2">
-        <v>46309.916666666664</v>
+        <v>46310.75</v>
       </c>
       <c r="L17" t="s">
         <v>43</v>
@@ -1806,34 +1794,34 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s">
         <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J18" s="2">
-        <v>46309.208333333336</v>
+        <v>46309.25</v>
       </c>
       <c r="K18" s="2">
-        <v>46310.75</v>
+        <v>46309.708333333336</v>
       </c>
       <c r="L18" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1847,13 +1835,13 @@
         <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
         <v>17</v>
@@ -1862,10 +1850,10 @@
         <v>25</v>
       </c>
       <c r="J19" s="2">
-        <v>46309.25</v>
+        <v>46309.541666666664</v>
       </c>
       <c r="K19" s="2">
-        <v>46309.708333333336</v>
+        <v>46310.041666666664</v>
       </c>
       <c r="L19" t="s">
         <v>26</v>
@@ -1873,37 +1861,37 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s">
         <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J20" s="2">
-        <v>46309.541666666664</v>
+        <v>46309.625</v>
       </c>
       <c r="K20" s="2">
-        <v>46310.041666666664</v>
+        <v>46311.75</v>
       </c>
       <c r="L20" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1911,28 +1899,28 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E21" s="1">
         <v>26165</v>
       </c>
       <c r="F21" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G21" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I21" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J21" s="2">
         <v>46309.625</v>
@@ -1946,37 +1934,37 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s">
         <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J22" s="2">
-        <v>46309.625</v>
+        <v>46309.75</v>
       </c>
       <c r="K22" s="2">
-        <v>46311.75</v>
+        <v>46310.666666666664</v>
       </c>
       <c r="L22" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1984,31 +1972,34 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
         <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>73</v>
+        <v>87</v>
+      </c>
+      <c r="E23" s="1">
+        <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="H23" t="s">
+        <v>89</v>
       </c>
       <c r="I23" t="s">
         <v>25</v>
       </c>
       <c r="J23" s="2">
-        <v>46309.75</v>
+        <v>46310.25</v>
       </c>
       <c r="K23" s="2">
-        <v>46310.666666666664</v>
+        <v>46310.75</v>
       </c>
       <c r="L23" t="s">
         <v>26</v>
@@ -2016,40 +2007,37 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" s="1">
-        <v>4</v>
+        <v>91</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="F24" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J24" s="2">
         <v>46310.25</v>
       </c>
       <c r="K24" s="2">
-        <v>46310.75</v>
+        <v>46311.166666666664</v>
       </c>
       <c r="L24" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2060,19 +2048,19 @@
         <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F25" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="I25" t="s">
         <v>18</v>
@@ -2081,7 +2069,7 @@
         <v>46310.25</v>
       </c>
       <c r="K25" s="2">
-        <v>46311.166666666664</v>
+        <v>46311.708333333336</v>
       </c>
       <c r="L25" t="s">
         <v>43</v>
@@ -2092,31 +2080,31 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="G26" t="s">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s">
         <v>18</v>
       </c>
       <c r="J26" s="2">
-        <v>46310.25</v>
+        <v>46310.291666666664</v>
       </c>
       <c r="K26" s="2">
-        <v>46311.708333333336</v>
+        <v>46311.166666666664</v>
       </c>
       <c r="L26" t="s">
         <v>43</v>
@@ -2124,34 +2112,37 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="F27" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>66</v>
+      </c>
+      <c r="H27" t="s">
+        <v>67</v>
       </c>
       <c r="I27" t="s">
         <v>18</v>
       </c>
       <c r="J27" s="2">
-        <v>46310.291666666664</v>
+        <v>46311.104166666664</v>
       </c>
       <c r="K27" s="2">
-        <v>46311.166666666664</v>
+        <v>46311.916666666664</v>
       </c>
       <c r="L27" t="s">
         <v>43</v>
@@ -2159,25 +2150,25 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="G28" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="H28" t="s">
         <v>67</v>
@@ -2186,10 +2177,10 @@
         <v>18</v>
       </c>
       <c r="J28" s="2">
-        <v>46311.104166666664</v>
+        <v>46311.25</v>
       </c>
       <c r="K28" s="2">
-        <v>46311.916666666664</v>
+        <v>46312.166666666664</v>
       </c>
       <c r="L28" t="s">
         <v>43</v>
@@ -2197,25 +2188,22 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F29" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="G29" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="H29" t="s">
         <v>67</v>
@@ -2224,10 +2212,10 @@
         <v>18</v>
       </c>
       <c r="J29" s="2">
-        <v>46311.25</v>
+        <v>46311.291666666664</v>
       </c>
       <c r="K29" s="2">
-        <v>46312.166666666664</v>
+        <v>46312.125</v>
       </c>
       <c r="L29" t="s">
         <v>43</v>
@@ -2238,34 +2226,37 @@
         <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="G30" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
         <v>67</v>
       </c>
       <c r="I30" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="J30" s="2">
-        <v>46311.291666666664</v>
+        <v>46311.541666666664</v>
       </c>
       <c r="K30" s="2">
-        <v>46312.125</v>
+        <v>46312.083333333336</v>
       </c>
       <c r="L30" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2273,37 +2264,37 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
+      </c>
+      <c r="E31" s="1">
+        <v>26164</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="G31" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="H31" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="I31" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="J31" s="2">
-        <v>46311.541666666664</v>
+        <v>46311.625</v>
       </c>
       <c r="K31" s="2">
-        <v>46312.083333333336</v>
+        <v>46312.041666666664</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2311,37 +2302,37 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>112</v>
-      </c>
-      <c r="E32" s="1">
-        <v>26164</v>
+        <v>108</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="F32" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="G32" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="I32" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="J32" s="2">
-        <v>46311.625</v>
+        <v>46312.125</v>
       </c>
       <c r="K32" s="2">
-        <v>46312.041666666664</v>
+        <v>46312.666666666664</v>
       </c>
       <c r="L32" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2349,69 +2340,66 @@
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="G33" t="s">
         <v>17</v>
       </c>
-      <c r="H33" t="s">
-        <v>67</v>
-      </c>
       <c r="I33" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="J33" s="2">
-        <v>46312.125</v>
+        <v>46312.5</v>
       </c>
       <c r="K33" s="2">
-        <v>46312.666666666664</v>
+        <v>46315.75</v>
       </c>
       <c r="L33" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F34" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
       <c r="G34" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="I34" t="s">
         <v>18</v>
       </c>
       <c r="J34" s="2">
-        <v>46312.5</v>
+        <v>46312.625</v>
       </c>
       <c r="K34" s="2">
-        <v>46315.75</v>
+        <v>46313.75</v>
       </c>
       <c r="L34" t="s">
         <v>43</v>
@@ -2419,22 +2407,22 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F35" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s">
         <v>17</v>
@@ -2443,10 +2431,10 @@
         <v>18</v>
       </c>
       <c r="J35" s="2">
-        <v>46312.5</v>
+        <v>46312.625</v>
       </c>
       <c r="K35" s="2">
-        <v>46315.75</v>
+        <v>46314.75</v>
       </c>
       <c r="L35" t="s">
         <v>43</v>
@@ -2454,107 +2442,107 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F36" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="G36" t="s">
         <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J36" s="2">
-        <v>46312.625</v>
+        <v>46314.25</v>
       </c>
       <c r="K36" s="2">
         <v>46314.75</v>
       </c>
       <c r="L36" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G37" t="s">
         <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J37" s="2">
-        <v>46312.625</v>
+        <v>46314.25</v>
       </c>
       <c r="K37" s="2">
         <v>46314.75</v>
       </c>
       <c r="L37" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F38" t="s">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="G38" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J38" s="2">
-        <v>46312.625</v>
+        <v>46314.25</v>
       </c>
       <c r="K38" s="2">
-        <v>46313.75</v>
+        <v>46314.75</v>
       </c>
       <c r="L38" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2564,29 +2552,29 @@
       <c r="B39" t="s">
         <v>37</v>
       </c>
-      <c r="C39" t="s">
-        <v>38</v>
-      </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="F39" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="G39" t="s">
-        <v>42</v>
+        <v>17</v>
+      </c>
+      <c r="H39" t="s">
+        <v>67</v>
       </c>
       <c r="I39" t="s">
         <v>18</v>
       </c>
       <c r="J39" s="2">
-        <v>46312.625</v>
+        <v>46314.625</v>
       </c>
       <c r="K39" s="2">
-        <v>46313.75</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L39" t="s">
         <v>43</v>
@@ -2597,34 +2585,34 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E40" s="1">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="F40" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="G40" t="s">
         <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J40" s="2">
-        <v>46314.25</v>
+        <v>46314.625</v>
       </c>
       <c r="K40" s="2">
-        <v>46314.75</v>
+        <v>46318.75</v>
       </c>
       <c r="L40" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2632,34 +2620,34 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="D41" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F41" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="G41" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="I41" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J41" s="2">
-        <v>46314.25</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K41" s="2">
-        <v>46314.75</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="L41" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2667,54 +2655,54 @@
         <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="D42" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="F42" t="s">
-        <v>127</v>
+        <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I42" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J42" s="2">
-        <v>46314.25</v>
+        <v>46315.25</v>
       </c>
       <c r="K42" s="2">
-        <v>46314.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L42" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>128</v>
-      </c>
-      <c r="E43" s="1">
-        <v>34</v>
+        <v>138</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="F43" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G43" t="s">
         <v>17</v>
@@ -2723,10 +2711,10 @@
         <v>18</v>
       </c>
       <c r="J43" s="2">
-        <v>46314.625</v>
+        <v>46315.291666666664</v>
       </c>
       <c r="K43" s="2">
-        <v>46318.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L43" t="s">
         <v>43</v>
@@ -2737,31 +2725,31 @@
         <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="C44" t="s">
+        <v>44</v>
       </c>
       <c r="D44" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="G44" t="s">
         <v>17</v>
       </c>
-      <c r="H44" t="s">
-        <v>67</v>
-      </c>
       <c r="I44" t="s">
         <v>18</v>
       </c>
       <c r="J44" s="2">
-        <v>46314.625</v>
+        <v>46315.708333333336</v>
       </c>
       <c r="K44" s="2">
-        <v>46315.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L44" t="s">
         <v>43</v>
@@ -2772,34 +2760,37 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
       <c r="D45" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F45" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="G45" t="s">
-        <v>135</v>
+        <v>66</v>
+      </c>
+      <c r="H45" t="s">
+        <v>67</v>
       </c>
       <c r="I45" t="s">
         <v>18</v>
       </c>
       <c r="J45" s="2">
-        <v>46315.208333333336</v>
+        <v>46316.104166666664</v>
       </c>
       <c r="K45" s="2">
-        <v>46316.791666666664</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L45" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2807,89 +2798,92 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C46" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>136</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>137</v>
+        <v>144</v>
+      </c>
+      <c r="E46" s="1">
+        <v>63</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G46" t="s">
         <v>24</v>
       </c>
       <c r="I46" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J46" s="2">
-        <v>46315.25</v>
+        <v>46316.25</v>
       </c>
       <c r="K46" s="2">
-        <v>46317.166666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L46" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F47" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="G47" t="s">
         <v>17</v>
       </c>
+      <c r="H47" t="s">
+        <v>36</v>
+      </c>
       <c r="I47" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J47" s="2">
-        <v>46315.291666666664</v>
+        <v>46316.25</v>
       </c>
       <c r="K47" s="2">
-        <v>46317.166666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L47" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="D48" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F48" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s">
         <v>17</v>
@@ -2898,10 +2892,10 @@
         <v>18</v>
       </c>
       <c r="J48" s="2">
-        <v>46315.708333333336</v>
+        <v>46316.625</v>
       </c>
       <c r="K48" s="2">
-        <v>46317.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L48" t="s">
         <v>43</v>
@@ -2912,37 +2906,37 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C49" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="D49" t="s">
-        <v>142</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>143</v>
+        <v>83</v>
+      </c>
+      <c r="E49" s="1">
+        <v>26169</v>
       </c>
       <c r="F49" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G49" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H49" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="I49" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J49" s="2">
-        <v>46316.104166666664</v>
+        <v>46316.625</v>
       </c>
       <c r="K49" s="2">
-        <v>46316.916666666664</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L49" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2950,37 +2944,34 @@
         <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="D50" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F50" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s">
         <v>17</v>
       </c>
-      <c r="H50" t="s">
-        <v>36</v>
-      </c>
       <c r="I50" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J50" s="2">
-        <v>46316.25</v>
+        <v>46316.625</v>
       </c>
       <c r="K50" s="2">
-        <v>46316.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L50" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2994,25 +2985,28 @@
         <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
-      </c>
-      <c r="E51" s="1">
-        <v>63</v>
+        <v>145</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="F51" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="G51" t="s">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="H51" t="s">
+        <v>36</v>
       </c>
       <c r="I51" t="s">
         <v>25</v>
       </c>
       <c r="J51" s="2">
-        <v>46316.25</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="K51" s="2">
-        <v>46316.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L51" t="s">
         <v>26</v>
@@ -3023,31 +3017,28 @@
         <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D52" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F52" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="G52" t="s">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="I52" t="s">
         <v>18</v>
       </c>
       <c r="J52" s="2">
-        <v>46316.625</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K52" s="2">
-        <v>46319.75</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L52" t="s">
         <v>43</v>
@@ -3055,37 +3046,34 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="C53" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="D53" t="s">
-        <v>79</v>
-      </c>
-      <c r="E53" s="1">
-        <v>26169</v>
+        <v>153</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="F53" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="G53" t="s">
-        <v>81</v>
-      </c>
-      <c r="H53" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="I53" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="J53" s="2">
-        <v>46316.625</v>
+        <v>46317.25</v>
       </c>
       <c r="K53" s="2">
-        <v>46317.041666666664</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L53" t="s">
         <v>43</v>
@@ -3093,69 +3081,63 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="D54" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F54" t="s">
-        <v>127</v>
-      </c>
-      <c r="G54" t="s">
-        <v>17</v>
-      </c>
-      <c r="H54" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I54" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J54" s="2">
-        <v>46316.791666666664</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K54" s="2">
-        <v>46317.75</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L54" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>37</v>
+      </c>
+      <c r="C55" t="s">
+        <v>157</v>
       </c>
       <c r="D55" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F55" t="s">
-        <v>134</v>
-      </c>
-      <c r="G55" t="s">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="I55" t="s">
         <v>18</v>
       </c>
       <c r="J55" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K55" s="2">
-        <v>46318.708333333336</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L55" t="s">
         <v>43</v>
@@ -3163,69 +3145,72 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="F56" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G56" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I56" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J56" s="2">
-        <v>46317.25</v>
+        <v>46318.25</v>
       </c>
       <c r="K56" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L56" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D57" t="s">
-        <v>155</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
+      </c>
+      <c r="E57" s="1">
+        <v>4</v>
       </c>
       <c r="F57" t="s">
-        <v>31</v>
+        <v>74</v>
+      </c>
+      <c r="G57" t="s">
+        <v>17</v>
       </c>
       <c r="I57" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J57" s="2">
-        <v>46317.291666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K57" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L57" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3236,25 +3221,25 @@
         <v>37</v>
       </c>
       <c r="C58" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="D58" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F58" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="I58" t="s">
         <v>18</v>
       </c>
       <c r="J58" s="2">
-        <v>46317.927777777775</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K58" s="2">
-        <v>46318.969444444447</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="L58" t="s">
         <v>43</v>
@@ -3265,31 +3250,34 @@
         <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C59" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="D59" t="s">
-        <v>160</v>
-      </c>
-      <c r="E59" s="1">
-        <v>4</v>
+        <v>165</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="F59" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="G59" t="s">
-        <v>17</v>
+        <v>66</v>
+      </c>
+      <c r="H59" t="s">
+        <v>67</v>
       </c>
       <c r="I59" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J59" s="2">
-        <v>46318.25</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K59" s="2">
-        <v>46318.75</v>
+        <v>46319.125</v>
       </c>
       <c r="L59" t="s">
         <v>26</v>
@@ -3297,37 +3285,34 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C60" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="D60" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F60" t="s">
-        <v>23</v>
-      </c>
-      <c r="G60" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="I60" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J60" s="2">
-        <v>46318.25</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K60" s="2">
-        <v>46318.75</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="L60" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3335,66 +3320,66 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C61" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D61" t="s">
-        <v>163</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>164</v>
+        <v>112</v>
+      </c>
+      <c r="E61" s="1">
+        <v>26168</v>
       </c>
       <c r="F61" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="G61" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="H61" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="I61" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J61" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.625</v>
       </c>
       <c r="K61" s="2">
-        <v>46319.125</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L61" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C62" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="D62" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>166</v>
       </c>
       <c r="F62" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="I62" t="s">
         <v>18</v>
       </c>
       <c r="J62" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K62" s="2">
-        <v>46319.666666666664</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L62" t="s">
         <v>43</v>
@@ -3405,37 +3390,34 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="C63" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="D63" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="E63" s="1">
-        <v>26168</v>
+        <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="G63" t="s">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="I63" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="J63" s="2">
-        <v>46318.625</v>
+        <v>46319.25</v>
       </c>
       <c r="K63" s="2">
-        <v>46319.041666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L63" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3443,31 +3425,34 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="C64" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="D64" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F64" t="s">
-        <v>66</v>
+        <v>127</v>
+      </c>
+      <c r="G64" t="s">
+        <v>17</v>
       </c>
       <c r="I64" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J64" s="2">
-        <v>46318.704861111109</v>
+        <v>46319.25</v>
       </c>
       <c r="K64" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.75</v>
       </c>
       <c r="L64" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3475,104 +3460,95 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="D65" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>127</v>
-      </c>
-      <c r="G65" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="I65" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J65" s="2">
-        <v>46319.25</v>
+        <v>46320</v>
       </c>
       <c r="K65" s="2">
-        <v>46319.75</v>
+        <v>46322</v>
       </c>
       <c r="L65" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="D66" t="s">
-        <v>170</v>
-      </c>
-      <c r="E66" s="1">
-        <v>1</v>
+        <v>174</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="F66" t="s">
-        <v>171</v>
-      </c>
-      <c r="G66" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="I66" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J66" s="2">
-        <v>46319.25</v>
+        <v>46320.21875</v>
       </c>
       <c r="K66" s="2">
-        <v>46322.75</v>
+        <v>46324.59375</v>
       </c>
       <c r="L66" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C67" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>170</v>
-      </c>
-      <c r="E67" s="1">
-        <v>1</v>
+        <v>176</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="F67" t="s">
-        <v>171</v>
-      </c>
-      <c r="G67" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I67" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J67" s="2">
-        <v>46319.25</v>
+        <v>46320.649305555555</v>
       </c>
       <c r="K67" s="2">
-        <v>46322.75</v>
+        <v>46321.149305555555</v>
       </c>
       <c r="L67" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3580,28 +3556,31 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="C68" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="D68" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F68" t="s">
-        <v>134</v>
+        <v>16</v>
+      </c>
+      <c r="G68" t="s">
+        <v>24</v>
       </c>
       <c r="I68" t="s">
         <v>18</v>
       </c>
       <c r="J68" s="2">
-        <v>46320</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K68" s="2">
-        <v>46322</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L68" t="s">
         <v>43</v>
@@ -3609,31 +3588,34 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C69" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="D69" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F69" t="s">
-        <v>86</v>
+        <v>16</v>
+      </c>
+      <c r="G69" t="s">
+        <v>24</v>
       </c>
       <c r="I69" t="s">
         <v>18</v>
       </c>
       <c r="J69" s="2">
-        <v>46320.21875</v>
+        <v>46321.25</v>
       </c>
       <c r="K69" s="2">
-        <v>46324.59375</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L69" t="s">
         <v>43</v>
@@ -3641,31 +3623,34 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>176</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
+      </c>
+      <c r="E70" s="1">
+        <v>21</v>
       </c>
       <c r="F70" t="s">
-        <v>31</v>
+        <v>16</v>
+      </c>
+      <c r="G70" t="s">
+        <v>17</v>
       </c>
       <c r="I70" t="s">
         <v>18</v>
       </c>
       <c r="J70" s="2">
-        <v>46320.649305555555</v>
+        <v>46321.625</v>
       </c>
       <c r="K70" s="2">
-        <v>46321.149305555555</v>
+        <v>46325.75</v>
       </c>
       <c r="L70" t="s">
         <v>43</v>
@@ -3676,66 +3661,57 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C71" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>178</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F71" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="G71" t="s">
         <v>24</v>
       </c>
+      <c r="H71" t="s">
+        <v>89</v>
+      </c>
       <c r="I71" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J71" s="2">
-        <v>46321.208333333336</v>
+        <v>46322.25</v>
       </c>
       <c r="K71" s="2">
-        <v>46323.166666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L71" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B72" t="s">
-        <v>50</v>
-      </c>
-      <c r="C72" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D72" t="s">
-        <v>180</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F72" t="s">
-        <v>16</v>
-      </c>
-      <c r="G72" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="I72" t="s">
         <v>18</v>
       </c>
       <c r="J72" s="2">
-        <v>46321.25</v>
+        <v>46322.256249999999</v>
       </c>
       <c r="K72" s="2">
-        <v>46323.166666666664</v>
+        <v>46323.381249999999</v>
       </c>
       <c r="L72" t="s">
         <v>43</v>
@@ -3746,31 +3722,28 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="D73" t="s">
-        <v>182</v>
-      </c>
-      <c r="E73" s="1">
-        <v>21</v>
+        <v>185</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="F73" t="s">
-        <v>16</v>
-      </c>
-      <c r="G73" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="I73" t="s">
         <v>18</v>
       </c>
       <c r="J73" s="2">
-        <v>46321.625</v>
+        <v>46322.388194444444</v>
       </c>
       <c r="K73" s="2">
-        <v>46325.75</v>
+        <v>46325.388194444444</v>
       </c>
       <c r="L73" t="s">
         <v>43</v>
@@ -3781,31 +3754,31 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C74" t="s">
         <v>21</v>
       </c>
       <c r="D74" t="s">
-        <v>183</v>
+        <v>187</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="F74" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="G74" t="s">
-        <v>24</v>
-      </c>
-      <c r="H74" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="I74" t="s">
         <v>25</v>
       </c>
       <c r="J74" s="2">
-        <v>46322.25</v>
+        <v>46323.25</v>
       </c>
       <c r="K74" s="2">
-        <v>46322.75</v>
+        <v>46323.75</v>
       </c>
       <c r="L74" t="s">
         <v>26</v>
@@ -3813,25 +3786,28 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>37</v>
+        <v>62</v>
+      </c>
+      <c r="C75" t="s">
+        <v>63</v>
       </c>
       <c r="D75" t="s">
-        <v>184</v>
+        <v>101</v>
       </c>
       <c r="F75" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I75" t="s">
         <v>18</v>
       </c>
       <c r="J75" s="2">
-        <v>46322.256249999999</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K75" s="2">
-        <v>46323.381249999999</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L75" t="s">
         <v>43</v>
@@ -3842,28 +3818,28 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>130</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="D76" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F76" t="s">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="I76" t="s">
         <v>18</v>
       </c>
       <c r="J76" s="2">
-        <v>46322.388194444444</v>
+        <v>46323.622916666667</v>
       </c>
       <c r="K76" s="2">
-        <v>46325.388194444444</v>
+        <v>46324.875</v>
       </c>
       <c r="L76" t="s">
         <v>43</v>
@@ -3874,34 +3850,37 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="D77" t="s">
-        <v>187</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>188</v>
+        <v>83</v>
+      </c>
+      <c r="E77" s="1">
+        <v>26173</v>
       </c>
       <c r="F77" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="G77" t="s">
-        <v>17</v>
+        <v>85</v>
+      </c>
+      <c r="H77" t="s">
+        <v>85</v>
       </c>
       <c r="I77" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="J77" s="2">
-        <v>46323.25</v>
+        <v>46323.625</v>
       </c>
       <c r="K77" s="2">
-        <v>46323.75</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L77" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3909,25 +3888,28 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>101</v>
+        <v>192</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="F78" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="I78" t="s">
         <v>18</v>
       </c>
       <c r="J78" s="2">
-        <v>46323.291666666664</v>
+        <v>46323.625</v>
       </c>
       <c r="K78" s="2">
-        <v>46323.791666666664</v>
+        <v>46327.541666666664</v>
       </c>
       <c r="L78" t="s">
         <v>43</v>
@@ -3941,25 +3923,25 @@
         <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>114</v>
+        <v>14</v>
       </c>
       <c r="D79" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F79" t="s">
-        <v>191</v>
+        <v>23</v>
       </c>
       <c r="I79" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="2">
-        <v>46323.622916666667</v>
+        <v>46323.625</v>
       </c>
       <c r="K79" s="2">
-        <v>46324.875</v>
+        <v>46327.541666666664</v>
       </c>
       <c r="L79" t="s">
         <v>43</v>
@@ -3970,34 +3952,28 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="C80" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D80" t="s">
-        <v>79</v>
-      </c>
-      <c r="E80" s="1">
-        <v>26173</v>
+        <v>194</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="F80" t="s">
-        <v>80</v>
-      </c>
-      <c r="G80" t="s">
-        <v>81</v>
-      </c>
-      <c r="H80" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="I80" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="J80" s="2">
-        <v>46323.625</v>
+        <v>46323.661111111112</v>
       </c>
       <c r="K80" s="2">
-        <v>46324.041666666664</v>
+        <v>46327.202777777777</v>
       </c>
       <c r="L80" t="s">
         <v>43</v>
@@ -4008,16 +3984,16 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D81" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F81" t="s">
         <v>23</v>
@@ -4026,10 +4002,10 @@
         <v>18</v>
       </c>
       <c r="J81" s="2">
-        <v>46323.625</v>
+        <v>46323.661111111112</v>
       </c>
       <c r="K81" s="2">
-        <v>46327.541666666664</v>
+        <v>46327.202777777777</v>
       </c>
       <c r="L81" t="s">
         <v>43</v>
@@ -4040,31 +4016,34 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D82" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F82" t="s">
         <v>23</v>
       </c>
+      <c r="G82" t="s">
+        <v>17</v>
+      </c>
       <c r="I82" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J82" s="2">
-        <v>46323.625</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K82" s="2">
-        <v>46327.541666666664</v>
+        <v>46324.75</v>
       </c>
       <c r="L82" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -4072,28 +4051,25 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>50</v>
-      </c>
-      <c r="C83" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="D83" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F83" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="I83" t="s">
         <v>18</v>
       </c>
       <c r="J83" s="2">
-        <v>46323.661111111112</v>
+        <v>46324</v>
       </c>
       <c r="K83" s="2">
-        <v>46327.202777777777</v>
+        <v>46326</v>
       </c>
       <c r="L83" t="s">
         <v>43</v>
@@ -4101,31 +4077,31 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D84" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F84" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I84" t="s">
         <v>18</v>
       </c>
       <c r="J84" s="2">
-        <v>46323.661111111112</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K84" s="2">
-        <v>46327.202777777777</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L84" t="s">
         <v>43</v>
@@ -4133,37 +4109,34 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C85" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="D85" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="F85" t="s">
-        <v>23</v>
-      </c>
-      <c r="G85" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="I85" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J85" s="2">
-        <v>46323.791666666664</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K85" s="2">
-        <v>46324.75</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L85" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4171,92 +4144,101 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>130</v>
+        <v>32</v>
+      </c>
+      <c r="C86" t="s">
+        <v>21</v>
       </c>
       <c r="D86" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F86" t="s">
-        <v>134</v>
+        <v>23</v>
+      </c>
+      <c r="G86" t="s">
+        <v>17</v>
       </c>
       <c r="I86" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J86" s="2">
-        <v>46324</v>
+        <v>46325.25</v>
       </c>
       <c r="K86" s="2">
-        <v>46326</v>
+        <v>46325.75</v>
       </c>
       <c r="L86" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="C87" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D87" t="s">
-        <v>198</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="F87" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="I87" t="s">
         <v>18</v>
       </c>
       <c r="J87" s="2">
-        <v>46325.003472222219</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K87" s="2">
-        <v>46325.878472222219</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L87" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="C88" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D88" t="s">
-        <v>200</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>201</v>
+        <v>112</v>
+      </c>
+      <c r="E88" s="1">
+        <v>26172</v>
       </c>
       <c r="F88" t="s">
-        <v>97</v>
+        <v>84</v>
+      </c>
+      <c r="G88" t="s">
+        <v>85</v>
+      </c>
+      <c r="H88" t="s">
+        <v>85</v>
       </c>
       <c r="I88" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J88" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.625</v>
       </c>
       <c r="K88" s="2">
-        <v>46326.098611111112</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L88" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4264,7 +4246,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C89" t="s">
         <v>21</v>
@@ -4285,10 +4267,10 @@
         <v>25</v>
       </c>
       <c r="J89" s="2">
-        <v>46325.25</v>
+        <v>46325.791666666664</v>
       </c>
       <c r="K89" s="2">
-        <v>46325.75</v>
+        <v>46326.75</v>
       </c>
       <c r="L89" t="s">
         <v>26</v>
@@ -4296,31 +4278,34 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>142</v>
+        <v>204</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F90" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="I90" t="s">
         <v>18</v>
       </c>
       <c r="J90" s="2">
-        <v>46325.333333333336</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K90" s="2">
-        <v>46325.833333333336</v>
+        <v>46328.125</v>
       </c>
       <c r="L90" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4328,37 +4313,34 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C91" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="D91" t="s">
-        <v>112</v>
-      </c>
-      <c r="E91" s="1">
-        <v>26172</v>
+        <v>206</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="F91" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="G91" t="s">
-        <v>81</v>
-      </c>
-      <c r="H91" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="I91" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="J91" s="2">
-        <v>46325.625</v>
+        <v>46326.25</v>
       </c>
       <c r="K91" s="2">
-        <v>46326.041666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L91" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4366,63 +4348,57 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="C92" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="D92" t="s">
-        <v>202</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>203</v>
+        <v>107</v>
       </c>
       <c r="F92" t="s">
-        <v>23</v>
-      </c>
-      <c r="G92" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="I92" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J92" s="2">
-        <v>46325.791666666664</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K92" s="2">
         <v>46326.75</v>
       </c>
       <c r="L92" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C93" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D93" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F93" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="I93" t="s">
         <v>18</v>
       </c>
       <c r="J93" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K93" s="2">
-        <v>46328.125</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L93" t="s">
         <v>43</v>
@@ -4433,28 +4409,28 @@
         <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C94" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D94" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F94" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="I94" t="s">
         <v>18</v>
       </c>
       <c r="J94" s="2">
-        <v>46326.166666666664</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K94" s="2">
-        <v>46328.125</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L94" t="s">
         <v>43</v>
@@ -4465,19 +4441,19 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C95" t="s">
         <v>21</v>
       </c>
       <c r="D95" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F95" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="G95" t="s">
         <v>17</v>
@@ -4486,10 +4462,10 @@
         <v>25</v>
       </c>
       <c r="J95" s="2">
-        <v>46326.25</v>
+        <v>46327.25</v>
       </c>
       <c r="K95" s="2">
-        <v>46326.75</v>
+        <v>46327.75</v>
       </c>
       <c r="L95" t="s">
         <v>26</v>
@@ -4497,28 +4473,25 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B96" t="s">
-        <v>62</v>
-      </c>
-      <c r="C96" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="D96" t="s">
-        <v>107</v>
+        <v>214</v>
       </c>
       <c r="F96" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I96" t="s">
         <v>18</v>
       </c>
       <c r="J96" s="2">
-        <v>46326.416666666664</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K96" s="2">
-        <v>46326.75</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L96" t="s">
         <v>43</v>
@@ -4529,31 +4502,34 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C97" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D97" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F97" t="s">
-        <v>191</v>
+        <v>127</v>
+      </c>
+      <c r="G97" t="s">
+        <v>17</v>
       </c>
       <c r="I97" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J97" s="2">
-        <v>46326.833333333336</v>
+        <v>46327.791666666664</v>
       </c>
       <c r="K97" s="2">
-        <v>46329.583333333336</v>
+        <v>46328.75</v>
       </c>
       <c r="L97" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4564,25 +4540,25 @@
         <v>50</v>
       </c>
       <c r="C98" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D98" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F98" t="s">
-        <v>191</v>
+        <v>23</v>
       </c>
       <c r="I98" t="s">
         <v>18</v>
       </c>
       <c r="J98" s="2">
-        <v>46326.833333333336</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K98" s="2">
-        <v>46329.583333333336</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L98" t="s">
         <v>43</v>
@@ -4590,31 +4566,31 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="F99" t="s">
-        <v>86</v>
+        <v>191</v>
       </c>
       <c r="I99" t="s">
         <v>18</v>
       </c>
       <c r="J99" s="2">
-        <v>46327.166666666664</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K99" s="2">
-        <v>46328.541666666664</v>
+        <v>46332.625</v>
       </c>
       <c r="L99" t="s">
         <v>43</v>
@@ -4622,60 +4598,57 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>32</v>
-      </c>
-      <c r="C100" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D100" t="s">
-        <v>212</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F100" t="s">
-        <v>127</v>
-      </c>
-      <c r="G100" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="I100" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J100" s="2">
-        <v>46327.25</v>
+        <v>46330.083333333336</v>
       </c>
       <c r="K100" s="2">
-        <v>46327.75</v>
+        <v>46331.208333333336</v>
       </c>
       <c r="L100" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>37</v>
+        <v>130</v>
+      </c>
+      <c r="C101" t="s">
+        <v>131</v>
       </c>
       <c r="D101" t="s">
-        <v>214</v>
+        <v>220</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="F101" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="I101" t="s">
         <v>18</v>
       </c>
       <c r="J101" s="2">
-        <v>46327.708333333336</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K101" s="2">
-        <v>46328.833333333336</v>
+        <v>46333.208333333336</v>
       </c>
       <c r="L101" t="s">
         <v>43</v>
@@ -4686,34 +4659,28 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="C102" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="D102" t="s">
-        <v>212</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="F102" t="s">
-        <v>127</v>
-      </c>
-      <c r="G102" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="I102" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="J102" s="2">
-        <v>46327.791666666664</v>
+        <v>46330.625</v>
       </c>
       <c r="K102" s="2">
-        <v>46328.75</v>
+        <v>46331.125</v>
       </c>
       <c r="L102" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4721,28 +4688,28 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F103" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="I103" t="s">
         <v>18</v>
       </c>
       <c r="J103" s="2">
-        <v>46327.904861111114</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K103" s="2">
-        <v>46331.196527777778</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L103" t="s">
         <v>43</v>
@@ -4759,10 +4726,10 @@
         <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F104" t="s">
         <v>191</v>
@@ -4771,10 +4738,10 @@
         <v>18</v>
       </c>
       <c r="J104" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K104" s="2">
-        <v>46332.625</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L104" t="s">
         <v>43</v>
@@ -4782,25 +4749,28 @@
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>37</v>
+        <v>62</v>
+      </c>
+      <c r="C105" t="s">
+        <v>63</v>
       </c>
       <c r="D105" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="F105" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I105" t="s">
         <v>18</v>
       </c>
       <c r="J105" s="2">
-        <v>46330.083333333336</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K105" s="2">
-        <v>46331.208333333336</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L105" t="s">
         <v>43</v>
@@ -4808,31 +4778,31 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="C106" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D106" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="I106" t="s">
         <v>18</v>
       </c>
       <c r="J106" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.75</v>
       </c>
       <c r="K106" s="2">
-        <v>46333.208333333336</v>
+        <v>46332.75</v>
       </c>
       <c r="L106" t="s">
         <v>43</v>
@@ -4840,28 +4810,31 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B107" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="C107" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D107" t="s">
-        <v>79</v>
+        <v>226</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="F107" t="s">
         <v>80</v>
       </c>
       <c r="I107" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="J107" s="2">
-        <v>46330.625</v>
+        <v>46331.020833333336</v>
       </c>
       <c r="K107" s="2">
-        <v>46331.125</v>
+        <v>46332.520833333336</v>
       </c>
       <c r="L107" t="s">
         <v>43</v>
@@ -4869,31 +4842,28 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B108" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C108" t="s">
-        <v>114</v>
+        <v>57</v>
       </c>
       <c r="D108" t="s">
-        <v>222</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F108" t="s">
-        <v>191</v>
+        <v>31</v>
       </c>
       <c r="I108" t="s">
         <v>18</v>
       </c>
       <c r="J108" s="2">
-        <v>46330.633333333331</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K108" s="2">
-        <v>46333.925000000003</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L108" t="s">
         <v>43</v>
@@ -4904,25 +4874,28 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C109" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D109" t="s">
-        <v>167</v>
+        <v>229</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="F109" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="I109" t="s">
         <v>18</v>
       </c>
       <c r="J109" s="2">
-        <v>46330.704861111109</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K109" s="2">
-        <v>46331.204861111109</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L109" t="s">
         <v>43</v>
@@ -4930,31 +4903,31 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C110" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F110" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="I110" t="s">
         <v>18</v>
       </c>
       <c r="J110" s="2">
-        <v>46330.75</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K110" s="2">
-        <v>46332.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L110" t="s">
         <v>43</v>
@@ -4968,25 +4941,25 @@
         <v>37</v>
       </c>
       <c r="C111" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="D111" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F111" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="I111" t="s">
         <v>18</v>
       </c>
       <c r="J111" s="2">
-        <v>46331.020833333336</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K111" s="2">
-        <v>46332.520833333336</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L111" t="s">
         <v>43</v>
@@ -4997,25 +4970,28 @@
         <v>27</v>
       </c>
       <c r="B112" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C112" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="D112" t="s">
-        <v>228</v>
+        <v>233</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="F112" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="I112" t="s">
         <v>18</v>
       </c>
       <c r="J112" s="2">
-        <v>46331.291666666664</v>
+        <v>46332.083333333336</v>
       </c>
       <c r="K112" s="2">
-        <v>46332.166666666664</v>
+        <v>46333.291666666664</v>
       </c>
       <c r="L112" t="s">
         <v>43</v>
@@ -5026,31 +5002,34 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C113" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D113" t="s">
-        <v>229</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>230</v>
+        <v>235</v>
+      </c>
+      <c r="E113" s="1">
+        <v>1</v>
       </c>
       <c r="F113" t="s">
-        <v>191</v>
+        <v>74</v>
+      </c>
+      <c r="G113" t="s">
+        <v>17</v>
       </c>
       <c r="I113" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J113" s="2">
-        <v>46331.496527777781</v>
+        <v>46332.25</v>
       </c>
       <c r="K113" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.75</v>
       </c>
       <c r="L113" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -5058,60 +5037,63 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C114" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D114" t="s">
-        <v>229</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
+      </c>
+      <c r="E114" s="1">
+        <v>10</v>
       </c>
       <c r="F114" t="s">
-        <v>191</v>
+        <v>74</v>
+      </c>
+      <c r="G114" t="s">
+        <v>17</v>
       </c>
       <c r="I114" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J114" s="2">
-        <v>46331.496527777781</v>
+        <v>46332.25</v>
       </c>
       <c r="K114" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.75</v>
       </c>
       <c r="L114" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>157</v>
+        <v>14</v>
       </c>
       <c r="D115" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F115" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="I115" t="s">
         <v>18</v>
       </c>
       <c r="J115" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.25</v>
       </c>
       <c r="K115" s="2">
-        <v>46332.597916666666</v>
+        <v>46336.041666666664</v>
       </c>
       <c r="L115" t="s">
         <v>43</v>
@@ -5119,31 +5101,31 @@
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C116" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D116" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F116" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I116" t="s">
         <v>18</v>
       </c>
       <c r="J116" s="2">
-        <v>46332.083333333336</v>
+        <v>46332.25</v>
       </c>
       <c r="K116" s="2">
-        <v>46333.291666666664</v>
+        <v>46336.041666666664</v>
       </c>
       <c r="L116" t="s">
         <v>43</v>
@@ -5154,34 +5136,28 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C117" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="D117" t="s">
-        <v>235</v>
-      </c>
-      <c r="E117" s="1">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="F117" t="s">
-        <v>74</v>
-      </c>
-      <c r="G117" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="I117" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J117" s="2">
-        <v>46332.25</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K117" s="2">
-        <v>46332.75</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L117" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -5189,307 +5165,28 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="C118" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="D118" t="s">
-        <v>236</v>
-      </c>
-      <c r="E118" s="1">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="F118" t="s">
-        <v>74</v>
-      </c>
-      <c r="G118" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="I118" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J118" s="2">
-        <v>46332.25</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K118" s="2">
-        <v>46332.75</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L118" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12">
-      <c r="A119" t="s">
-        <v>12</v>
-      </c>
-      <c r="B119" t="s">
-        <v>13</v>
-      </c>
-      <c r="C119" t="s">
-        <v>14</v>
-      </c>
-      <c r="D119" t="s">
-        <v>237</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F119" t="s">
-        <v>23</v>
-      </c>
-      <c r="I119" t="s">
-        <v>18</v>
-      </c>
-      <c r="J119" s="2">
-        <v>46332.25</v>
-      </c>
-      <c r="K119" s="2">
-        <v>46336.041666666664</v>
-      </c>
-      <c r="L119" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12">
-      <c r="A120" t="s">
-        <v>12</v>
-      </c>
-      <c r="B120" t="s">
-        <v>13</v>
-      </c>
-      <c r="C120" t="s">
-        <v>14</v>
-      </c>
-      <c r="D120" t="s">
-        <v>237</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F120" t="s">
-        <v>23</v>
-      </c>
-      <c r="I120" t="s">
-        <v>18</v>
-      </c>
-      <c r="J120" s="2">
-        <v>46332.25</v>
-      </c>
-      <c r="K120" s="2">
-        <v>46336.041666666664</v>
-      </c>
-      <c r="L120" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12">
-      <c r="A121" t="s">
-        <v>12</v>
-      </c>
-      <c r="B121" t="s">
-        <v>62</v>
-      </c>
-      <c r="C121" t="s">
-        <v>63</v>
-      </c>
-      <c r="D121" t="s">
-        <v>101</v>
-      </c>
-      <c r="F121" t="s">
-        <v>66</v>
-      </c>
-      <c r="I121" t="s">
-        <v>18</v>
-      </c>
-      <c r="J121" s="2">
-        <v>46332.291666666664</v>
-      </c>
-      <c r="K121" s="2">
-        <v>46332.791666666664</v>
-      </c>
-      <c r="L121" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12">
-      <c r="A122" t="s">
-        <v>12</v>
-      </c>
-      <c r="B122" t="s">
-        <v>77</v>
-      </c>
-      <c r="C122" t="s">
-        <v>111</v>
-      </c>
-      <c r="D122" t="s">
-        <v>112</v>
-      </c>
-      <c r="F122" t="s">
-        <v>80</v>
-      </c>
-      <c r="I122" t="s">
-        <v>18</v>
-      </c>
-      <c r="J122" s="2">
-        <v>46332.541666666664</v>
-      </c>
-      <c r="K122" s="2">
-        <v>46333.041666666664</v>
-      </c>
-      <c r="L122" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12">
-      <c r="A123" t="s">
-        <v>12</v>
-      </c>
-      <c r="B123" t="s">
-        <v>130</v>
-      </c>
-      <c r="D123" t="s">
-        <v>239</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F123" t="s">
-        <v>134</v>
-      </c>
-      <c r="I123" t="s">
-        <v>18</v>
-      </c>
-      <c r="J123" s="2">
-        <v>46333.041666666664</v>
-      </c>
-      <c r="K123" s="2">
-        <v>46335.041666666664</v>
-      </c>
-      <c r="L123" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12">
-      <c r="A124" t="s">
-        <v>12</v>
-      </c>
-      <c r="B124" t="s">
-        <v>130</v>
-      </c>
-      <c r="D124" t="s">
-        <v>239</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F124" t="s">
-        <v>134</v>
-      </c>
-      <c r="I124" t="s">
-        <v>18</v>
-      </c>
-      <c r="J124" s="2">
-        <v>46333.041666666664</v>
-      </c>
-      <c r="K124" s="2">
-        <v>46335.041666666664</v>
-      </c>
-      <c r="L124" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12">
-      <c r="A125" t="s">
-        <v>12</v>
-      </c>
-      <c r="B125" t="s">
-        <v>62</v>
-      </c>
-      <c r="C125" t="s">
-        <v>106</v>
-      </c>
-      <c r="D125" t="s">
-        <v>163</v>
-      </c>
-      <c r="F125" t="s">
-        <v>66</v>
-      </c>
-      <c r="I125" t="s">
-        <v>18</v>
-      </c>
-      <c r="J125" s="2">
-        <v>46333.416666666664</v>
-      </c>
-      <c r="K125" s="2">
-        <v>46333.75</v>
-      </c>
-      <c r="L125" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12">
-      <c r="A126" t="s">
-        <v>27</v>
-      </c>
-      <c r="B126" t="s">
-        <v>37</v>
-      </c>
-      <c r="C126" t="s">
-        <v>83</v>
-      </c>
-      <c r="D126" t="s">
-        <v>241</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F126" t="s">
-        <v>86</v>
-      </c>
-      <c r="I126" t="s">
-        <v>18</v>
-      </c>
-      <c r="J126" s="2">
-        <v>46333.666666666664</v>
-      </c>
-      <c r="K126" s="2">
-        <v>46335.041666666664</v>
-      </c>
-      <c r="L126" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12">
-      <c r="A127" t="s">
-        <v>27</v>
-      </c>
-      <c r="B127" t="s">
-        <v>37</v>
-      </c>
-      <c r="C127" t="s">
-        <v>83</v>
-      </c>
-      <c r="D127" t="s">
-        <v>241</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F127" t="s">
-        <v>86</v>
-      </c>
-      <c r="I127" t="s">
-        <v>18</v>
-      </c>
-      <c r="J127" s="2">
-        <v>46333.666666666664</v>
-      </c>
-      <c r="K127" s="2">
-        <v>46335.041666666664</v>
-      </c>
-      <c r="L127" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -5501,6 +5198,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5638,41 +5358,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
--- a/data/vessels/2026-10-11.xlsx
+++ b/data/vessels/2026-10-11.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="416027" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{245621A7-B2E6-4FD6-90A2-3EAC3EFB2EF5}"/>
+  <xr:revisionPtr revIDLastSave="416521" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7201667-938E-4920-AAF0-337A4BBB67B0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="239">
   <si>
     <t>Harbor</t>
   </si>
@@ -137,126 +137,126 @@
     <t>MSC</t>
   </si>
   <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>XIN SHAN TOU</t>
+  </si>
+  <si>
+    <t>225N/225E</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>In transit</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>EXPRESS ATHENS</t>
+  </si>
+  <si>
+    <t>UK638R</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>WISDOM ACE</t>
+  </si>
+  <si>
+    <t>104A</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
+    <t>MORNING LISA</t>
+  </si>
+  <si>
+    <t>KW662</t>
+  </si>
+  <si>
+    <t>Eukor</t>
+  </si>
+  <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>ONE MAESTRO</t>
+  </si>
+  <si>
+    <t>088W</t>
+  </si>
+  <si>
+    <t>SM SEOUL</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>MSC PINA</t>
+  </si>
+  <si>
+    <t>UK639R</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>MSC BOSTON</t>
+  </si>
+  <si>
+    <t>MC641R</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>641S</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>HYUNDAI SUPREME</t>
+  </si>
+  <si>
+    <t>PN32635E</t>
+  </si>
+  <si>
+    <t>HMM</t>
+  </si>
+  <si>
     <t>EB1</t>
   </si>
   <si>
-    <t>MORNING LISA</t>
-  </si>
-  <si>
-    <t>KW662</t>
-  </si>
-  <si>
-    <t>Eukor</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>T18</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>XIN SHAN TOU</t>
-  </si>
-  <si>
-    <t>225N/225E</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>In transit</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>EXPRESS ATHENS</t>
-  </si>
-  <si>
-    <t>UK638R</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>WISDOM ACE</t>
-  </si>
-  <si>
-    <t>104A</t>
-  </si>
-  <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>ONE MAESTRO</t>
-  </si>
-  <si>
-    <t>088W</t>
-  </si>
-  <si>
-    <t>SM SEOUL</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>MSC BOSTON</t>
-  </si>
-  <si>
-    <t>MC641R</t>
-  </si>
-  <si>
-    <t>MSC PINA</t>
-  </si>
-  <si>
-    <t>UK639R</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>641S</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>HYUNDAI SUPREME</t>
-  </si>
-  <si>
-    <t>PN32635E</t>
-  </si>
-  <si>
-    <t>HMM</t>
-  </si>
-  <si>
     <t>RCC TIANJIN</t>
   </si>
   <si>
@@ -380,7 +380,7 @@
     <t>NORTH STAR</t>
   </si>
   <si>
-    <t>Waiting 3.7 days</t>
+    <t>Waiting 3.9 days</t>
   </si>
   <si>
     <t>WC4/TP5</t>
@@ -395,16 +395,28 @@
     <t>Maersk</t>
   </si>
   <si>
+    <t>CMA CGM ALMAVIVA</t>
+  </si>
+  <si>
+    <t>CPN02/CPN03</t>
+  </si>
+  <si>
     <t>XIN YING KOU</t>
   </si>
   <si>
     <t>269N/269S</t>
   </si>
   <si>
-    <t>CMA CGM ALMAVIVA</t>
-  </si>
-  <si>
-    <t>CPN02/CPN03</t>
+    <t>MODERN LINK</t>
+  </si>
+  <si>
+    <t>THEMISA</t>
+  </si>
+  <si>
+    <t>ED615</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
   </si>
   <si>
     <t>SALVIA ACE</t>
@@ -413,18 +425,6 @@
     <t>177A</t>
   </si>
   <si>
-    <t>MODERN LINK</t>
-  </si>
-  <si>
-    <t>THEMISA</t>
-  </si>
-  <si>
-    <t>ED615</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
     <t>SM QINGDAO</t>
   </si>
   <si>
@@ -545,16 +545,16 @@
     <t>RJ PFEIFFER</t>
   </si>
   <si>
+    <t>ARC HONOR</t>
+  </si>
+  <si>
+    <t>ED616</t>
+  </si>
+  <si>
     <t>ARC INDEPENDENCE</t>
   </si>
   <si>
     <t>ARC</t>
-  </si>
-  <si>
-    <t>ARC HONOR</t>
-  </si>
-  <si>
-    <t>ED616</t>
   </si>
   <si>
     <t>EVER SALUTE</t>
@@ -828,10 +828,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L118" totalsRowShown="0">
-  <autoFilter ref="A1:L118" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L118">
-    <sortCondition ref="J2:J118"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L117" totalsRowShown="0">
+  <autoFilter ref="A1:L117" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L117">
+    <sortCondition ref="J2:J117"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L118"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1397,40 +1397,37 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J7" s="2">
         <v>46306.25</v>
       </c>
       <c r="K7" s="2">
-        <v>46306.583333333336</v>
+        <v>46307.166666666664</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1438,69 +1435,72 @@
         <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
       <c r="J8" s="2">
-        <v>46306.25</v>
+        <v>46306.291666666664</v>
       </c>
       <c r="K8" s="2">
-        <v>46307.166666666664</v>
+        <v>46308.166666666664</v>
       </c>
       <c r="L8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
       </c>
+      <c r="H9" t="s">
+        <v>45</v>
+      </c>
       <c r="I9" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J9" s="2">
-        <v>46306.291666666664</v>
+        <v>46306.541666666664</v>
       </c>
       <c r="K9" s="2">
-        <v>46308.166666666664</v>
+        <v>46306.999305555553</v>
       </c>
       <c r="L9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1508,34 +1508,34 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>
       </c>
       <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
         <v>48</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" t="s">
-        <v>23</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="I10" t="s">
         <v>25</v>
       </c>
       <c r="J10" s="2">
-        <v>46306.541666666664</v>
+        <v>46306.625</v>
       </c>
       <c r="K10" s="2">
-        <v>46306.999305555553</v>
+        <v>46307.166666666664</v>
       </c>
       <c r="L10" t="s">
         <v>26</v>
@@ -1546,57 +1546,51 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
         <v>17</v>
       </c>
-      <c r="H11" t="s">
-        <v>36</v>
-      </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J11" s="2">
         <v>46306.625</v>
       </c>
       <c r="K11" s="2">
-        <v>46307.166666666664</v>
+        <v>46308.75</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
         <v>17</v>
@@ -1605,13 +1599,13 @@
         <v>18</v>
       </c>
       <c r="J12" s="2">
-        <v>46306.625</v>
+        <v>46307.25</v>
       </c>
       <c r="K12" s="2">
-        <v>46308.75</v>
+        <v>46307.75</v>
       </c>
       <c r="L12" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1619,16 +1613,19 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="G13" t="s">
         <v>17</v>
@@ -1637,13 +1634,13 @@
         <v>18</v>
       </c>
       <c r="J13" s="2">
-        <v>46307.25</v>
+        <v>46308.291666666664</v>
       </c>
       <c r="K13" s="2">
-        <v>46307.75</v>
+        <v>46310.166666666664</v>
       </c>
       <c r="L13" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1654,13 +1651,13 @@
         <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
         <v>31</v>
@@ -1678,42 +1675,45 @@
         <v>46309.75</v>
       </c>
       <c r="L14" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>65</v>
+      </c>
+      <c r="H15" t="s">
+        <v>66</v>
       </c>
       <c r="I15" t="s">
         <v>18</v>
       </c>
       <c r="J15" s="2">
-        <v>46308.291666666664</v>
+        <v>46309.104166666664</v>
       </c>
       <c r="K15" s="2">
-        <v>46310.166666666664</v>
+        <v>46309.916666666664</v>
       </c>
       <c r="L15" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1721,37 +1721,34 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="I16" t="s">
         <v>18</v>
       </c>
       <c r="J16" s="2">
-        <v>46309.104166666664</v>
+        <v>46309.208333333336</v>
       </c>
       <c r="K16" s="2">
-        <v>46309.916666666664</v>
+        <v>46310.75</v>
       </c>
       <c r="L16" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1759,34 +1756,34 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s">
         <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J17" s="2">
-        <v>46309.208333333336</v>
+        <v>46309.25</v>
       </c>
       <c r="K17" s="2">
-        <v>46310.75</v>
+        <v>46309.708333333336</v>
       </c>
       <c r="L17" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1794,19 +1791,19 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="G18" t="s">
         <v>17</v>
@@ -1815,10 +1812,10 @@
         <v>25</v>
       </c>
       <c r="J18" s="2">
-        <v>46309.25</v>
+        <v>46309.541666666664</v>
       </c>
       <c r="K18" s="2">
-        <v>46309.708333333336</v>
+        <v>46310.041666666664</v>
       </c>
       <c r="L18" t="s">
         <v>26</v>
@@ -1826,72 +1823,75 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s">
         <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J19" s="2">
-        <v>46309.541666666664</v>
+        <v>46309.625</v>
       </c>
       <c r="K19" s="2">
-        <v>46310.041666666664</v>
+        <v>46311.75</v>
       </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
+      </c>
+      <c r="E20" s="1">
+        <v>26165</v>
       </c>
       <c r="F20" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>85</v>
+      </c>
+      <c r="H20" t="s">
+        <v>85</v>
       </c>
       <c r="I20" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J20" s="2">
         <v>46309.625</v>
       </c>
       <c r="K20" s="2">
-        <v>46311.75</v>
+        <v>46310.041666666664</v>
       </c>
       <c r="L20" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1899,37 +1899,34 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="1">
-        <v>26165</v>
+        <v>72</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="F21" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
-      </c>
-      <c r="H21" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="J21" s="2">
-        <v>46309.625</v>
+        <v>46309.75</v>
       </c>
       <c r="K21" s="2">
-        <v>46310.041666666664</v>
+        <v>46310.666666666664</v>
       </c>
       <c r="L21" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1937,31 +1934,34 @@
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>73</v>
+        <v>87</v>
+      </c>
+      <c r="E22" s="1">
+        <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="H22" t="s">
+        <v>89</v>
       </c>
       <c r="I22" t="s">
         <v>25</v>
       </c>
       <c r="J22" s="2">
-        <v>46309.75</v>
+        <v>46310.25</v>
       </c>
       <c r="K22" s="2">
-        <v>46310.666666666664</v>
+        <v>46310.75</v>
       </c>
       <c r="L22" t="s">
         <v>26</v>
@@ -1969,40 +1969,37 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23" s="1">
-        <v>4</v>
+        <v>91</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="F23" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J23" s="2">
         <v>46310.25</v>
       </c>
       <c r="K23" s="2">
-        <v>46310.75</v>
+        <v>46311.166666666664</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2010,22 +2007,22 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F24" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G24" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="I24" t="s">
         <v>18</v>
@@ -2034,10 +2031,10 @@
         <v>46310.25</v>
       </c>
       <c r="K24" s="2">
-        <v>46311.166666666664</v>
+        <v>46311.708333333336</v>
       </c>
       <c r="L24" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2045,145 +2042,145 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F25" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="G25" t="s">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
         <v>18</v>
       </c>
       <c r="J25" s="2">
-        <v>46310.25</v>
+        <v>46310.291666666664</v>
       </c>
       <c r="K25" s="2">
-        <v>46311.708333333336</v>
+        <v>46311.166666666664</v>
       </c>
       <c r="L25" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="F26" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>65</v>
+      </c>
+      <c r="H26" t="s">
+        <v>66</v>
       </c>
       <c r="I26" t="s">
         <v>18</v>
       </c>
       <c r="J26" s="2">
-        <v>46310.291666666664</v>
+        <v>46311.104166666664</v>
       </c>
       <c r="K26" s="2">
-        <v>46311.166666666664</v>
+        <v>46311.916666666664</v>
       </c>
       <c r="L26" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="F27" t="s">
+        <v>105</v>
+      </c>
+      <c r="G27" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" t="s">
         <v>66</v>
       </c>
-      <c r="G27" t="s">
-        <v>66</v>
-      </c>
-      <c r="H27" t="s">
-        <v>67</v>
-      </c>
       <c r="I27" t="s">
         <v>18</v>
       </c>
       <c r="J27" s="2">
-        <v>46311.104166666664</v>
+        <v>46311.25</v>
       </c>
       <c r="K27" s="2">
-        <v>46311.916666666664</v>
+        <v>46312.166666666664</v>
       </c>
       <c r="L27" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D28" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F28" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="G28" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="H28" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I28" t="s">
         <v>18</v>
       </c>
       <c r="J28" s="2">
-        <v>46311.25</v>
+        <v>46311.291666666664</v>
       </c>
       <c r="K28" s="2">
-        <v>46312.166666666664</v>
+        <v>46312.125</v>
       </c>
       <c r="L28" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2191,34 +2188,37 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="F29" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" t="s">
         <v>66</v>
       </c>
-      <c r="G29" t="s">
-        <v>66</v>
-      </c>
-      <c r="H29" t="s">
-        <v>67</v>
-      </c>
       <c r="I29" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="J29" s="2">
-        <v>46311.291666666664</v>
+        <v>46311.541666666664</v>
       </c>
       <c r="K29" s="2">
-        <v>46312.125</v>
+        <v>46312.083333333336</v>
       </c>
       <c r="L29" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2226,37 +2226,37 @@
         <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
+      </c>
+      <c r="E30" s="1">
+        <v>26164</v>
       </c>
       <c r="F30" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="G30" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="H30" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="I30" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="J30" s="2">
-        <v>46311.541666666664</v>
+        <v>46311.625</v>
       </c>
       <c r="K30" s="2">
-        <v>46312.083333333336</v>
+        <v>46312.041666666664</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2264,37 +2264,37 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
-      </c>
-      <c r="E31" s="1">
-        <v>26164</v>
+        <v>108</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="F31" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="G31" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="H31" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="I31" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="J31" s="2">
-        <v>46311.625</v>
+        <v>46312.125</v>
       </c>
       <c r="K31" s="2">
-        <v>46312.041666666664</v>
+        <v>46312.666666666664</v>
       </c>
       <c r="L31" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2302,57 +2302,54 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="G32" t="s">
         <v>17</v>
       </c>
-      <c r="H32" t="s">
-        <v>67</v>
-      </c>
       <c r="I32" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="J32" s="2">
-        <v>46312.125</v>
+        <v>46312.5</v>
       </c>
       <c r="K32" s="2">
-        <v>46312.666666666664</v>
+        <v>46315.75</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F33" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s">
         <v>17</v>
@@ -2361,13 +2358,13 @@
         <v>18</v>
       </c>
       <c r="J33" s="2">
-        <v>46312.5</v>
+        <v>46312.625</v>
       </c>
       <c r="K33" s="2">
-        <v>46315.75</v>
+        <v>46314.75</v>
       </c>
       <c r="L33" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2375,22 +2372,22 @@
         <v>27</v>
       </c>
       <c r="B34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" t="s">
+        <v>120</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F34" t="s">
+        <v>36</v>
+      </c>
+      <c r="G34" t="s">
         <v>37</v>
-      </c>
-      <c r="C34" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34" t="s">
-        <v>118</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F34" t="s">
-        <v>41</v>
-      </c>
-      <c r="G34" t="s">
-        <v>42</v>
       </c>
       <c r="I34" t="s">
         <v>18</v>
@@ -2402,42 +2399,42 @@
         <v>46313.75</v>
       </c>
       <c r="L34" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="D35" t="s">
-        <v>120</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s">
         <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J35" s="2">
-        <v>46312.625</v>
+        <v>46314.25</v>
       </c>
       <c r="K35" s="2">
         <v>46314.75</v>
       </c>
       <c r="L35" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2445,19 +2442,19 @@
         <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="C36" t="s">
         <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F36" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="G36" t="s">
         <v>17</v>
@@ -2480,19 +2477,19 @@
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
         <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>124</v>
-      </c>
-      <c r="E37" s="1">
-        <v>2</v>
+        <v>126</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="F37" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="G37" t="s">
         <v>17</v>
@@ -2512,61 +2509,61 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
         <v>32</v>
       </c>
-      <c r="C38" t="s">
-        <v>21</v>
-      </c>
       <c r="D38" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="F38" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="G38" t="s">
         <v>17</v>
       </c>
+      <c r="H38" t="s">
+        <v>66</v>
+      </c>
       <c r="I38" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J38" s="2">
-        <v>46314.25</v>
+        <v>46314.625</v>
       </c>
       <c r="K38" s="2">
-        <v>46314.75</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>13</v>
+      </c>
+      <c r="C39" t="s">
+        <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>128</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>55</v>
+        <v>129</v>
+      </c>
+      <c r="E39" s="1">
+        <v>34</v>
       </c>
       <c r="F39" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="G39" t="s">
         <v>17</v>
       </c>
-      <c r="H39" t="s">
-        <v>67</v>
-      </c>
       <c r="I39" t="s">
         <v>18</v>
       </c>
@@ -2574,10 +2571,10 @@
         <v>46314.625</v>
       </c>
       <c r="K39" s="2">
-        <v>46315.166666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L39" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2585,34 +2582,34 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
-      </c>
-      <c r="E40" s="1">
-        <v>34</v>
+        <v>132</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="F40" t="s">
-        <v>23</v>
+        <v>134</v>
       </c>
       <c r="G40" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="I40" t="s">
         <v>18</v>
       </c>
       <c r="J40" s="2">
-        <v>46314.625</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K40" s="2">
-        <v>46318.75</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="L40" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2620,69 +2617,69 @@
         <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F41" t="s">
-        <v>134</v>
+        <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="I41" t="s">
         <v>18</v>
       </c>
       <c r="J41" s="2">
-        <v>46315.208333333336</v>
+        <v>46315.25</v>
       </c>
       <c r="K41" s="2">
-        <v>46316.791666666664</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L41" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D42" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G42" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I42" t="s">
         <v>18</v>
       </c>
       <c r="J42" s="2">
-        <v>46315.25</v>
+        <v>46315.291666666664</v>
       </c>
       <c r="K42" s="2">
         <v>46317.166666666664</v>
       </c>
       <c r="L42" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2693,13 +2690,13 @@
         <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F43" t="s">
         <v>31</v>
@@ -2711,48 +2708,51 @@
         <v>18</v>
       </c>
       <c r="J43" s="2">
-        <v>46315.291666666664</v>
+        <v>46315.708333333336</v>
       </c>
       <c r="K43" s="2">
-        <v>46317.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L43" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D44" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="G44" t="s">
-        <v>17</v>
+        <v>65</v>
+      </c>
+      <c r="H44" t="s">
+        <v>66</v>
       </c>
       <c r="I44" t="s">
         <v>18</v>
       </c>
       <c r="J44" s="2">
-        <v>46315.708333333336</v>
+        <v>46316.104166666664</v>
       </c>
       <c r="K44" s="2">
-        <v>46317.75</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L44" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2760,34 +2760,31 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C45" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" t="s">
+        <v>144</v>
+      </c>
+      <c r="E45" s="1">
         <v>63</v>
       </c>
-      <c r="D45" t="s">
-        <v>142</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="F45" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="G45" t="s">
-        <v>66</v>
-      </c>
-      <c r="H45" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="I45" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J45" s="2">
-        <v>46316.104166666664</v>
+        <v>46316.25</v>
       </c>
       <c r="K45" s="2">
-        <v>46316.916666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L45" t="s">
         <v>26</v>
@@ -2798,22 +2795,25 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C46" t="s">
         <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>144</v>
-      </c>
-      <c r="E46" s="1">
-        <v>63</v>
+        <v>145</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="F46" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="G46" t="s">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="H46" t="s">
+        <v>45</v>
       </c>
       <c r="I46" t="s">
         <v>25</v>
@@ -2833,37 +2833,37 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="C47" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="D47" t="s">
-        <v>145</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>146</v>
+        <v>83</v>
+      </c>
+      <c r="E47" s="1">
+        <v>26169</v>
       </c>
       <c r="F47" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="G47" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="I47" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="J47" s="2">
-        <v>46316.25</v>
+        <v>46316.625</v>
       </c>
       <c r="K47" s="2">
-        <v>46316.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L47" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2898,7 +2898,7 @@
         <v>46319.75</v>
       </c>
       <c r="L48" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2906,37 +2906,34 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="D49" t="s">
-        <v>83</v>
-      </c>
-      <c r="E49" s="1">
-        <v>26169</v>
+        <v>147</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="F49" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s">
-        <v>85</v>
-      </c>
-      <c r="H49" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J49" s="2">
         <v>46316.625</v>
       </c>
       <c r="K49" s="2">
-        <v>46317.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L49" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2944,34 +2941,37 @@
         <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C50" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F50" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="G50" t="s">
         <v>17</v>
       </c>
+      <c r="H50" t="s">
+        <v>45</v>
+      </c>
       <c r="I50" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J50" s="2">
-        <v>46316.625</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="K50" s="2">
-        <v>46319.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L50" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2979,69 +2979,66 @@
         <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
-      </c>
-      <c r="C51" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="D51" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F51" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="G51" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" t="s">
-        <v>36</v>
+        <v>152</v>
       </c>
       <c r="I51" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J51" s="2">
-        <v>46316.791666666664</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K51" s="2">
-        <v>46317.75</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L51" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>130</v>
+        <v>32</v>
+      </c>
+      <c r="C52" t="s">
+        <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F52" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
       <c r="G52" t="s">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="I52" t="s">
         <v>18</v>
       </c>
       <c r="J52" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.25</v>
       </c>
       <c r="K52" s="2">
-        <v>46318.708333333336</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L52" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -3049,34 +3046,31 @@
         <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D53" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F53" t="s">
-        <v>41</v>
-      </c>
-      <c r="G53" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="I53" t="s">
         <v>18</v>
       </c>
       <c r="J53" s="2">
-        <v>46317.25</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K53" s="2">
         <v>46318.166666666664</v>
       </c>
       <c r="L53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3084,63 +3078,66 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C54" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F54" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="I54" t="s">
         <v>18</v>
       </c>
       <c r="J54" s="2">
-        <v>46317.291666666664</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K54" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L54" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="C55" t="s">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F55" t="s">
-        <v>97</v>
+        <v>23</v>
+      </c>
+      <c r="G55" t="s">
+        <v>17</v>
       </c>
       <c r="I55" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J55" s="2">
-        <v>46317.927777777775</v>
+        <v>46318.25</v>
       </c>
       <c r="K55" s="2">
-        <v>46318.969444444447</v>
+        <v>46318.75</v>
       </c>
       <c r="L55" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3148,19 +3145,19 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="C56" t="s">
         <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>160</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
+      </c>
+      <c r="E56" s="1">
+        <v>4</v>
       </c>
       <c r="F56" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="G56" t="s">
         <v>17</v>
@@ -3180,57 +3177,60 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B57" t="s">
         <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="D57" t="s">
-        <v>162</v>
-      </c>
-      <c r="E57" s="1">
-        <v>4</v>
+        <v>163</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="F57" t="s">
-        <v>74</v>
-      </c>
-      <c r="G57" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="I57" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J57" s="2">
-        <v>46318.25</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K57" s="2">
-        <v>46318.75</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="L57" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C58" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D58" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>105</v>
+        <v>65</v>
+      </c>
+      <c r="G58" t="s">
+        <v>65</v>
+      </c>
+      <c r="H58" t="s">
+        <v>66</v>
       </c>
       <c r="I58" t="s">
         <v>18</v>
@@ -3239,36 +3239,30 @@
         <v>46318.291666666664</v>
       </c>
       <c r="K58" s="2">
-        <v>46319.666666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L58" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="C59" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D59" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F59" t="s">
-        <v>66</v>
-      </c>
-      <c r="G59" t="s">
-        <v>66</v>
-      </c>
-      <c r="H59" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="I59" t="s">
         <v>18</v>
@@ -3277,42 +3271,48 @@
         <v>46318.291666666664</v>
       </c>
       <c r="K59" s="2">
-        <v>46319.125</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="L59" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="C60" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D60" t="s">
-        <v>163</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>164</v>
+        <v>112</v>
+      </c>
+      <c r="E60" s="1">
+        <v>26168</v>
       </c>
       <c r="F60" t="s">
-        <v>105</v>
+        <v>84</v>
+      </c>
+      <c r="G60" t="s">
+        <v>85</v>
+      </c>
+      <c r="H60" t="s">
+        <v>85</v>
       </c>
       <c r="I60" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J60" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.625</v>
       </c>
       <c r="K60" s="2">
-        <v>46319.666666666664</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L60" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3320,37 +3320,31 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="C61" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="D61" t="s">
-        <v>112</v>
-      </c>
-      <c r="E61" s="1">
-        <v>26168</v>
+        <v>167</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="F61" t="s">
-        <v>84</v>
-      </c>
-      <c r="G61" t="s">
-        <v>85</v>
-      </c>
-      <c r="H61" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="I61" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J61" s="2">
-        <v>46318.625</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K61" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L61" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3358,31 +3352,34 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C62" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="D62" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F62" t="s">
-        <v>66</v>
+        <v>125</v>
+      </c>
+      <c r="G62" t="s">
+        <v>17</v>
       </c>
       <c r="I62" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J62" s="2">
-        <v>46318.704861111109</v>
+        <v>46319.25</v>
       </c>
       <c r="K62" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.75</v>
       </c>
       <c r="L62" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3396,13 +3393,13 @@
         <v>21</v>
       </c>
       <c r="D63" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G63" t="s">
         <v>17</v>
@@ -3425,66 +3422,63 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="C64" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="D64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F64" t="s">
-        <v>127</v>
-      </c>
-      <c r="G64" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="I64" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J64" s="2">
-        <v>46319.25</v>
+        <v>46320</v>
       </c>
       <c r="K64" s="2">
-        <v>46319.75</v>
+        <v>46322</v>
       </c>
       <c r="L64" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="C65" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="D65" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F65" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="I65" t="s">
         <v>18</v>
       </c>
       <c r="J65" s="2">
-        <v>46320</v>
+        <v>46320.21875</v>
       </c>
       <c r="K65" s="2">
-        <v>46322</v>
+        <v>46324.59375</v>
       </c>
       <c r="L65" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3492,63 +3486,66 @@
         <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C66" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="D66" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F66" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="I66" t="s">
         <v>18</v>
       </c>
       <c r="J66" s="2">
-        <v>46320.21875</v>
+        <v>46320.649305555555</v>
       </c>
       <c r="K66" s="2">
-        <v>46324.59375</v>
+        <v>46321.149305555555</v>
       </c>
       <c r="L66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D67" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F67" t="s">
-        <v>31</v>
+        <v>16</v>
+      </c>
+      <c r="G67" t="s">
+        <v>24</v>
       </c>
       <c r="I67" t="s">
         <v>18</v>
       </c>
       <c r="J67" s="2">
-        <v>46320.649305555555</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K67" s="2">
-        <v>46321.149305555555</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L67" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3556,16 +3553,16 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
+        <v>49</v>
+      </c>
+      <c r="C68" t="s">
         <v>50</v>
       </c>
-      <c r="C68" t="s">
-        <v>68</v>
-      </c>
       <c r="D68" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F68" t="s">
         <v>16</v>
@@ -3577,13 +3574,13 @@
         <v>18</v>
       </c>
       <c r="J68" s="2">
-        <v>46321.208333333336</v>
+        <v>46321.25</v>
       </c>
       <c r="K68" s="2">
         <v>46323.166666666664</v>
       </c>
       <c r="L68" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3591,34 +3588,34 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>180</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="E69" s="1">
+        <v>21</v>
       </c>
       <c r="F69" t="s">
         <v>16</v>
       </c>
       <c r="G69" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I69" t="s">
         <v>18</v>
       </c>
       <c r="J69" s="2">
-        <v>46321.25</v>
+        <v>46321.625</v>
       </c>
       <c r="K69" s="2">
-        <v>46323.166666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L69" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3626,95 +3623,92 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>182</v>
-      </c>
-      <c r="E70" s="1">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="F70" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="G70" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="H70" t="s">
+        <v>89</v>
       </c>
       <c r="I70" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J70" s="2">
-        <v>46321.625</v>
+        <v>46322.25</v>
       </c>
       <c r="K70" s="2">
-        <v>46325.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L70" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B71" t="s">
-        <v>47</v>
-      </c>
-      <c r="C71" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D71" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F71" t="s">
-        <v>88</v>
-      </c>
-      <c r="G71" t="s">
-        <v>24</v>
-      </c>
-      <c r="H71" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="I71" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J71" s="2">
-        <v>46322.25</v>
+        <v>46322.256249999999</v>
       </c>
       <c r="K71" s="2">
-        <v>46322.75</v>
+        <v>46323.381249999999</v>
       </c>
       <c r="L71" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>37</v>
+        <v>130</v>
+      </c>
+      <c r="C72" t="s">
+        <v>131</v>
       </c>
       <c r="D72" t="s">
-        <v>184</v>
+        <v>185</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="F72" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="I72" t="s">
         <v>18</v>
       </c>
       <c r="J72" s="2">
-        <v>46322.256249999999</v>
+        <v>46322.388194444444</v>
       </c>
       <c r="K72" s="2">
-        <v>46323.381249999999</v>
+        <v>46325.388194444444</v>
       </c>
       <c r="L72" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3722,31 +3716,34 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="D73" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F73" t="s">
-        <v>134</v>
+        <v>23</v>
+      </c>
+      <c r="G73" t="s">
+        <v>17</v>
       </c>
       <c r="I73" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J73" s="2">
-        <v>46322.388194444444</v>
+        <v>46323.25</v>
       </c>
       <c r="K73" s="2">
-        <v>46325.388194444444</v>
+        <v>46323.75</v>
       </c>
       <c r="L73" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3754,34 +3751,28 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C74" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D74" t="s">
-        <v>187</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>188</v>
+        <v>101</v>
       </c>
       <c r="F74" t="s">
-        <v>23</v>
-      </c>
-      <c r="G74" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I74" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J74" s="2">
-        <v>46323.25</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K74" s="2">
-        <v>46323.75</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L74" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3789,28 +3780,31 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>101</v>
+        <v>189</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="F75" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="I75" t="s">
         <v>18</v>
       </c>
       <c r="J75" s="2">
-        <v>46323.291666666664</v>
+        <v>46323.622916666667</v>
       </c>
       <c r="K75" s="2">
-        <v>46323.791666666664</v>
+        <v>46324.875</v>
       </c>
       <c r="L75" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3818,31 +3812,37 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="C76" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="D76" t="s">
-        <v>189</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>190</v>
+        <v>83</v>
+      </c>
+      <c r="E76" s="1">
+        <v>26173</v>
       </c>
       <c r="F76" t="s">
-        <v>191</v>
+        <v>84</v>
+      </c>
+      <c r="G76" t="s">
+        <v>85</v>
+      </c>
+      <c r="H76" t="s">
+        <v>85</v>
       </c>
       <c r="I76" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J76" s="2">
-        <v>46323.622916666667</v>
+        <v>46323.625</v>
       </c>
       <c r="K76" s="2">
-        <v>46324.875</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L76" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3850,37 +3850,31 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>83</v>
-      </c>
-      <c r="E77" s="1">
-        <v>26173</v>
+        <v>192</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="F77" t="s">
-        <v>84</v>
-      </c>
-      <c r="G77" t="s">
-        <v>85</v>
-      </c>
-      <c r="H77" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="I77" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J77" s="2">
         <v>46323.625</v>
       </c>
       <c r="K77" s="2">
-        <v>46324.041666666664</v>
+        <v>46327.541666666664</v>
       </c>
       <c r="L77" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3912,7 +3906,7 @@
         <v>46327.541666666664</v>
       </c>
       <c r="L78" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3920,16 +3914,16 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D79" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F79" t="s">
         <v>23</v>
@@ -3938,13 +3932,13 @@
         <v>18</v>
       </c>
       <c r="J79" s="2">
-        <v>46323.625</v>
+        <v>46323.661111111112</v>
       </c>
       <c r="K79" s="2">
-        <v>46327.541666666664</v>
+        <v>46327.202777777777</v>
       </c>
       <c r="L79" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3952,10 +3946,10 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C80" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D80" t="s">
         <v>194</v>
@@ -3976,7 +3970,7 @@
         <v>46327.202777777777</v>
       </c>
       <c r="L80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3984,31 +3978,34 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C81" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="D81" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F81" t="s">
         <v>23</v>
       </c>
+      <c r="G81" t="s">
+        <v>17</v>
+      </c>
       <c r="I81" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J81" s="2">
-        <v>46323.661111111112</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K81" s="2">
-        <v>46327.202777777777</v>
+        <v>46324.75</v>
       </c>
       <c r="L81" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -4016,63 +4013,60 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>47</v>
-      </c>
-      <c r="C82" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="D82" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="F82" t="s">
-        <v>23</v>
-      </c>
-      <c r="G82" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="I82" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J82" s="2">
-        <v>46323.791666666664</v>
+        <v>46324</v>
       </c>
       <c r="K82" s="2">
-        <v>46324.75</v>
+        <v>46326</v>
       </c>
       <c r="L82" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>130</v>
+        <v>28</v>
+      </c>
+      <c r="C83" t="s">
+        <v>58</v>
       </c>
       <c r="D83" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F83" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="I83" t="s">
         <v>18</v>
       </c>
       <c r="J83" s="2">
-        <v>46324</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K83" s="2">
-        <v>46326</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4080,63 +4074,66 @@
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C84" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D84" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F84" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="I84" t="s">
         <v>18</v>
       </c>
       <c r="J84" s="2">
-        <v>46325.003472222219</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K84" s="2">
-        <v>46325.878472222219</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="C85" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="D85" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F85" t="s">
-        <v>97</v>
+        <v>23</v>
+      </c>
+      <c r="G85" t="s">
+        <v>17</v>
       </c>
       <c r="I85" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J85" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.25</v>
       </c>
       <c r="K85" s="2">
-        <v>46326.098611111112</v>
+        <v>46325.75</v>
       </c>
       <c r="L85" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4144,31 +4141,25 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C86" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D86" t="s">
-        <v>202</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>203</v>
+        <v>142</v>
       </c>
       <c r="F86" t="s">
-        <v>23</v>
-      </c>
-      <c r="G86" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I86" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J86" s="2">
-        <v>46325.25</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K86" s="2">
-        <v>46325.75</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L86" t="s">
         <v>26</v>
@@ -4179,28 +4170,37 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C87" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="D87" t="s">
-        <v>142</v>
+        <v>112</v>
+      </c>
+      <c r="E87" s="1">
+        <v>26172</v>
       </c>
       <c r="F87" t="s">
-        <v>66</v>
+        <v>84</v>
+      </c>
+      <c r="G87" t="s">
+        <v>85</v>
+      </c>
+      <c r="H87" t="s">
+        <v>85</v>
       </c>
       <c r="I87" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J87" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.625</v>
       </c>
       <c r="K87" s="2">
-        <v>46325.833333333336</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L87" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4208,104 +4208,101 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="C88" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="D88" t="s">
-        <v>112</v>
-      </c>
-      <c r="E88" s="1">
-        <v>26172</v>
+        <v>202</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F88" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="G88" t="s">
-        <v>85</v>
-      </c>
-      <c r="H88" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="I88" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="J88" s="2">
-        <v>46325.625</v>
+        <v>46325.791666666664</v>
       </c>
       <c r="K88" s="2">
-        <v>46326.041666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L88" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B89" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C89" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D89" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F89" t="s">
-        <v>23</v>
-      </c>
-      <c r="G89" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I89" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J89" s="2">
-        <v>46325.791666666664</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K89" s="2">
-        <v>46326.75</v>
+        <v>46328.125</v>
       </c>
       <c r="L89" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="D90" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F90" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="G90" t="s">
+        <v>17</v>
       </c>
       <c r="I90" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J90" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K90" s="2">
-        <v>46328.125</v>
+        <v>46326.75</v>
       </c>
       <c r="L90" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4313,34 +4310,28 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C91" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="D91" t="s">
-        <v>206</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>207</v>
+        <v>107</v>
       </c>
       <c r="F91" t="s">
-        <v>23</v>
-      </c>
-      <c r="G91" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I91" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J91" s="2">
-        <v>46326.25</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K91" s="2">
         <v>46326.75</v>
       </c>
       <c r="L91" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4348,153 +4339,159 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C92" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="D92" t="s">
-        <v>107</v>
+        <v>208</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="F92" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="I92" t="s">
         <v>18</v>
       </c>
       <c r="J92" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K92" s="2">
-        <v>46326.75</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L92" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B93" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C93" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D93" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F93" t="s">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="I93" t="s">
         <v>18</v>
       </c>
       <c r="J93" s="2">
-        <v>46326.833333333336</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K93" s="2">
-        <v>46329.583333333336</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L93" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="C94" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="D94" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F94" t="s">
-        <v>80</v>
+        <v>125</v>
+      </c>
+      <c r="G94" t="s">
+        <v>17</v>
       </c>
       <c r="I94" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J94" s="2">
-        <v>46327.166666666664</v>
+        <v>46327.25</v>
       </c>
       <c r="K94" s="2">
-        <v>46328.541666666664</v>
+        <v>46327.75</v>
       </c>
       <c r="L94" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B95" t="s">
         <v>32</v>
       </c>
-      <c r="C95" t="s">
-        <v>21</v>
-      </c>
       <c r="D95" t="s">
-        <v>212</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F95" t="s">
-        <v>127</v>
-      </c>
-      <c r="G95" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="I95" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J95" s="2">
-        <v>46327.25</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K95" s="2">
-        <v>46327.75</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L95" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>37</v>
+        <v>42</v>
+      </c>
+      <c r="C96" t="s">
+        <v>21</v>
       </c>
       <c r="D96" t="s">
-        <v>214</v>
+        <v>212</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="F96" t="s">
-        <v>56</v>
+        <v>125</v>
+      </c>
+      <c r="G96" t="s">
+        <v>17</v>
       </c>
       <c r="I96" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J96" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.791666666664</v>
       </c>
       <c r="K96" s="2">
-        <v>46328.833333333336</v>
+        <v>46328.75</v>
       </c>
       <c r="L96" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4502,34 +4499,31 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C97" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D97" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F97" t="s">
-        <v>127</v>
-      </c>
-      <c r="G97" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I97" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J97" s="2">
-        <v>46327.791666666664</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K97" s="2">
-        <v>46328.75</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L97" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4537,89 +4531,89 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F98" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="I98" t="s">
         <v>18</v>
       </c>
       <c r="J98" s="2">
-        <v>46327.904861111114</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K98" s="2">
-        <v>46331.196527777778</v>
+        <v>46332.625</v>
       </c>
       <c r="L98" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
-      </c>
-      <c r="C99" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="D99" t="s">
-        <v>217</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F99" t="s">
-        <v>191</v>
+        <v>55</v>
       </c>
       <c r="I99" t="s">
         <v>18</v>
       </c>
       <c r="J99" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.083333333336</v>
       </c>
       <c r="K99" s="2">
-        <v>46332.625</v>
+        <v>46331.208333333336</v>
       </c>
       <c r="L99" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>37</v>
+        <v>130</v>
+      </c>
+      <c r="C100" t="s">
+        <v>131</v>
       </c>
       <c r="D100" t="s">
-        <v>219</v>
+        <v>220</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="F100" t="s">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="I100" t="s">
         <v>18</v>
       </c>
       <c r="J100" s="2">
-        <v>46330.083333333336</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K100" s="2">
-        <v>46331.208333333336</v>
+        <v>46333.208333333336</v>
       </c>
       <c r="L100" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4627,31 +4621,28 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="C101" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="D101" t="s">
-        <v>220</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="F101" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="I101" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="J101" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.625</v>
       </c>
       <c r="K101" s="2">
-        <v>46333.208333333336</v>
+        <v>46331.125</v>
       </c>
       <c r="L101" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4659,28 +4650,31 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>83</v>
+        <v>222</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="F102" t="s">
-        <v>84</v>
+        <v>191</v>
       </c>
       <c r="I102" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J102" s="2">
-        <v>46330.625</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K102" s="2">
-        <v>46331.125</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L102" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4712,7 +4706,7 @@
         <v>46333.925000000003</v>
       </c>
       <c r="L103" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4720,60 +4714,60 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="C104" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="D104" t="s">
-        <v>222</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="F104" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="I104" t="s">
         <v>18</v>
       </c>
       <c r="J104" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K104" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L104" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B105" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="C105" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D105" t="s">
-        <v>167</v>
+        <v>224</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F105" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="I105" t="s">
         <v>18</v>
       </c>
       <c r="J105" s="2">
-        <v>46330.704861111109</v>
+        <v>46330.75</v>
       </c>
       <c r="K105" s="2">
-        <v>46331.204861111109</v>
+        <v>46332.75</v>
       </c>
       <c r="L105" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -4781,31 +4775,31 @@
         <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C106" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D106" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F106" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="I106" t="s">
         <v>18</v>
       </c>
       <c r="J106" s="2">
-        <v>46330.75</v>
+        <v>46331.020833333336</v>
       </c>
       <c r="K106" s="2">
-        <v>46332.75</v>
+        <v>46332.520833333336</v>
       </c>
       <c r="L106" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -4813,60 +4807,60 @@
         <v>27</v>
       </c>
       <c r="B107" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C107" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="D107" t="s">
-        <v>226</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F107" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="I107" t="s">
         <v>18</v>
       </c>
       <c r="J107" s="2">
-        <v>46331.020833333336</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K107" s="2">
-        <v>46332.520833333336</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L107" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C108" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D108" t="s">
-        <v>228</v>
+        <v>229</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="F108" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="I108" t="s">
         <v>18</v>
       </c>
       <c r="J108" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K108" s="2">
-        <v>46332.166666666664</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L108" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -4874,10 +4868,10 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
+        <v>49</v>
+      </c>
+      <c r="C109" t="s">
         <v>50</v>
-      </c>
-      <c r="C109" t="s">
-        <v>51</v>
       </c>
       <c r="D109" t="s">
         <v>229</v>
@@ -4898,39 +4892,39 @@
         <v>46334.746527777781</v>
       </c>
       <c r="L109" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B110" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C110" t="s">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="D110" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F110" t="s">
-        <v>191</v>
+        <v>97</v>
       </c>
       <c r="I110" t="s">
         <v>18</v>
       </c>
       <c r="J110" s="2">
-        <v>46331.496527777781</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K110" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L110" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -4938,63 +4932,66 @@
         <v>27</v>
       </c>
       <c r="B111" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C111" t="s">
-        <v>157</v>
+        <v>33</v>
       </c>
       <c r="D111" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F111" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="I111" t="s">
         <v>18</v>
       </c>
       <c r="J111" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.083333333336</v>
       </c>
       <c r="K111" s="2">
-        <v>46332.597916666666</v>
+        <v>46333.291666666664</v>
       </c>
       <c r="L111" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C112" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D112" t="s">
-        <v>233</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
+      </c>
+      <c r="E112" s="1">
+        <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>41</v>
+        <v>74</v>
+      </c>
+      <c r="G112" t="s">
+        <v>17</v>
       </c>
       <c r="I112" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J112" s="2">
-        <v>46332.083333333336</v>
+        <v>46332.25</v>
       </c>
       <c r="K112" s="2">
-        <v>46333.291666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L112" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -5002,16 +4999,16 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C113" t="s">
         <v>21</v>
       </c>
       <c r="D113" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E113" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F113" t="s">
         <v>74</v>
@@ -5037,34 +5034,31 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>236</v>
-      </c>
-      <c r="E114" s="1">
-        <v>10</v>
+        <v>237</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="F114" t="s">
-        <v>74</v>
-      </c>
-      <c r="G114" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I114" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J114" s="2">
         <v>46332.25</v>
       </c>
       <c r="K114" s="2">
-        <v>46332.75</v>
+        <v>46336.041666666664</v>
       </c>
       <c r="L114" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -5096,7 +5090,7 @@
         <v>46336.041666666664</v>
       </c>
       <c r="L115" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -5104,31 +5098,28 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="C116" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="D116" t="s">
-        <v>237</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>238</v>
+        <v>101</v>
       </c>
       <c r="F116" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="I116" t="s">
         <v>18</v>
       </c>
       <c r="J116" s="2">
-        <v>46332.25</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K116" s="2">
-        <v>46336.041666666664</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L116" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -5136,56 +5127,27 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C117" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="D117" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="F117" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="I117" t="s">
         <v>18</v>
       </c>
       <c r="J117" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K117" s="2">
-        <v>46332.791666666664</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L117" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12">
-      <c r="A118" t="s">
-        <v>12</v>
-      </c>
-      <c r="B118" t="s">
-        <v>81</v>
-      </c>
-      <c r="C118" t="s">
-        <v>111</v>
-      </c>
-      <c r="D118" t="s">
-        <v>112</v>
-      </c>
-      <c r="F118" t="s">
-        <v>84</v>
-      </c>
-      <c r="I118" t="s">
-        <v>18</v>
-      </c>
-      <c r="J118" s="2">
-        <v>46332.541666666664</v>
-      </c>
-      <c r="K118" s="2">
-        <v>46333.041666666664</v>
-      </c>
-      <c r="L118" t="s">
         <v>113</v>
       </c>
     </row>
@@ -5198,29 +5160,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5358,18 +5303,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
--- a/data/vessels/2026-10-11.xlsx
+++ b/data/vessels/2026-10-11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="416521" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7201667-938E-4920-AAF0-337A4BBB67B0}"/>
+  <xr:revisionPtr revIDLastSave="417022" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66EB8AB9-7FBB-40FD-AE93-FED90CC938B8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -311,6 +311,21 @@
     <t>Pacific Terminals</t>
   </si>
   <si>
+    <t>EB Service 2</t>
+  </si>
+  <si>
+    <t>SUVA CHIEF</t>
+  </si>
+  <si>
+    <t>007E/008W</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>Talon Marine Services LLC</t>
+  </si>
+  <si>
     <t>Oceania</t>
   </si>
   <si>
@@ -323,21 +338,6 @@
     <t>Hapag-Lloyd</t>
   </si>
   <si>
-    <t>EB Service 2</t>
-  </si>
-  <si>
-    <t>SUVA CHIEF</t>
-  </si>
-  <si>
-    <t>007E/008W</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>Talon Marine Services LLC</t>
-  </si>
-  <si>
     <t>CAPE TAINARO</t>
   </si>
   <si>
@@ -380,7 +380,7 @@
     <t>NORTH STAR</t>
   </si>
   <si>
-    <t>Waiting 3.9 days</t>
+    <t>Waiting 4.1 days</t>
   </si>
   <si>
     <t>WC4/TP5</t>
@@ -473,15 +473,15 @@
     <t>643S</t>
   </si>
   <si>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
     <t>THEMIS LEADER</t>
   </si>
   <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
     <t>VIENNA EXPRESS</t>
   </si>
   <si>
@@ -521,25 +521,25 @@
     <t>159E</t>
   </si>
   <si>
+    <t>POLARIS MILA</t>
+  </si>
+  <si>
     <t>CARNATION ACE</t>
   </si>
   <si>
     <t>107A</t>
   </si>
   <si>
-    <t>POLARIS MILA</t>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>642S</t>
   </si>
   <si>
     <t>OOCL SAN FRANCISCO</t>
   </si>
   <si>
     <t>199E</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
-    <t>642S</t>
   </si>
   <si>
     <t>RJ PFEIFFER</t>
@@ -1987,7 +1987,7 @@
         <v>93</v>
       </c>
       <c r="G23" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="I23" t="s">
         <v>18</v>
@@ -1996,7 +1996,7 @@
         <v>46310.25</v>
       </c>
       <c r="K23" s="2">
-        <v>46311.166666666664</v>
+        <v>46311.708333333336</v>
       </c>
       <c r="L23" t="s">
         <v>38</v>
@@ -2010,19 +2010,19 @@
         <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G24" t="s">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
         <v>18</v>
@@ -2031,7 +2031,7 @@
         <v>46310.25</v>
       </c>
       <c r="K24" s="2">
-        <v>46311.708333333336</v>
+        <v>46311.166666666664</v>
       </c>
       <c r="L24" t="s">
         <v>38</v>
@@ -2760,7 +2760,7 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C45" t="s">
         <v>21</v>
@@ -2768,14 +2768,17 @@
       <c r="D45" t="s">
         <v>144</v>
       </c>
-      <c r="E45" s="1">
-        <v>63</v>
+      <c r="E45" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="F45" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="G45" t="s">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="H45" t="s">
+        <v>45</v>
       </c>
       <c r="I45" t="s">
         <v>25</v>
@@ -2795,25 +2798,22 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C46" t="s">
         <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>145</v>
-      </c>
-      <c r="E46" s="1" t="s">
         <v>146</v>
       </c>
+      <c r="E46" s="1">
+        <v>63</v>
+      </c>
       <c r="F46" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="G46" t="s">
-        <v>17</v>
-      </c>
-      <c r="H46" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="I46" t="s">
         <v>25</v>
@@ -2883,7 +2883,7 @@
         <v>148</v>
       </c>
       <c r="F48" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G48" t="s">
         <v>17</v>
@@ -2918,7 +2918,7 @@
         <v>148</v>
       </c>
       <c r="F49" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G49" t="s">
         <v>17</v>
@@ -2947,7 +2947,7 @@
         <v>21</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>149</v>
@@ -3090,7 +3090,7 @@
         <v>159</v>
       </c>
       <c r="F54" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I54" t="s">
         <v>18</v>
@@ -3118,11 +3118,11 @@
       <c r="D55" t="s">
         <v>160</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>161</v>
+      <c r="E55" s="1">
+        <v>4</v>
       </c>
       <c r="F55" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="G55" t="s">
         <v>17</v>
@@ -3151,13 +3151,13 @@
         <v>21</v>
       </c>
       <c r="D56" t="s">
+        <v>161</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E56" s="1">
-        <v>4</v>
-      </c>
       <c r="F56" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="G56" t="s">
         <v>17</v>
@@ -3177,13 +3177,13 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D57" t="s">
         <v>163</v>
@@ -3192,7 +3192,13 @@
         <v>164</v>
       </c>
       <c r="F57" t="s">
-        <v>105</v>
+        <v>65</v>
+      </c>
+      <c r="G57" t="s">
+        <v>65</v>
+      </c>
+      <c r="H57" t="s">
+        <v>66</v>
       </c>
       <c r="I57" t="s">
         <v>18</v>
@@ -3201,21 +3207,21 @@
         <v>46318.291666666664</v>
       </c>
       <c r="K57" s="2">
-        <v>46319.666666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L57" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C58" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D58" t="s">
         <v>165</v>
@@ -3224,13 +3230,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>65</v>
-      </c>
-      <c r="G58" t="s">
-        <v>65</v>
-      </c>
-      <c r="H58" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="I58" t="s">
         <v>18</v>
@@ -3239,10 +3239,10 @@
         <v>46318.291666666664</v>
       </c>
       <c r="K58" s="2">
-        <v>46319.125</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="L58" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3256,10 +3256,10 @@
         <v>102</v>
       </c>
       <c r="D59" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F59" t="s">
         <v>105</v>
@@ -3329,7 +3329,7 @@
         <v>167</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F61" t="s">
         <v>65</v>
@@ -4077,7 +4077,7 @@
         <v>32</v>
       </c>
       <c r="C84" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D84" t="s">
         <v>200</v>
@@ -4086,7 +4086,7 @@
         <v>201</v>
       </c>
       <c r="F84" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I84" t="s">
         <v>18</v>
@@ -4778,7 +4778,7 @@
         <v>32</v>
       </c>
       <c r="C106" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D106" t="s">
         <v>226</v>
@@ -4912,7 +4912,7 @@
         <v>232</v>
       </c>
       <c r="F110" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I110" t="s">
         <v>18</v>
@@ -5160,12 +5160,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5303,35 +5320,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
--- a/data/vessels/2026-10-11.xlsx
+++ b/data/vessels/2026-10-11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="417022" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66EB8AB9-7FBB-40FD-AE93-FED90CC938B8}"/>
+  <xr:revisionPtr revIDLastSave="417522" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B5EECD9-DC4D-42AC-9EFE-D4D1B4AAD93D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="236">
   <si>
     <t>Harbor</t>
   </si>
@@ -167,141 +167,135 @@
     <t>UK638R</t>
   </si>
   <si>
+    <t>MORNING LISA</t>
+  </si>
+  <si>
+    <t>KW662</t>
+  </si>
+  <si>
+    <t>Eukor</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>ONE MAESTRO</t>
+  </si>
+  <si>
+    <t>088W</t>
+  </si>
+  <si>
+    <t>SM SEOUL</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>MSC PINA</t>
+  </si>
+  <si>
+    <t>UK639R</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>MSC BOSTON</t>
+  </si>
+  <si>
+    <t>MC641R</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>641S</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>HYUNDAI SUPREME</t>
+  </si>
+  <si>
+    <t>PN32635E</t>
+  </si>
+  <si>
+    <t>HMM</t>
+  </si>
+  <si>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>RCC TIANJIN</t>
+  </si>
+  <si>
+    <t>018A</t>
+  </si>
+  <si>
+    <t>Hyundai Glovis</t>
+  </si>
+  <si>
+    <t>BERGAMOT ACE</t>
+  </si>
+  <si>
+    <t>158A</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM BYBLOS</t>
+  </si>
+  <si>
+    <t>CPN00/CPN01</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
     <t>Blair</t>
   </si>
   <si>
-    <t>WISDOM ACE</t>
-  </si>
-  <si>
-    <t>104A</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>MORNING LISA</t>
-  </si>
-  <si>
-    <t>KW662</t>
-  </si>
-  <si>
-    <t>Eukor</t>
-  </si>
-  <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>ONE MAESTRO</t>
-  </si>
-  <si>
-    <t>088W</t>
-  </si>
-  <si>
-    <t>SM SEOUL</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>MSC PINA</t>
-  </si>
-  <si>
-    <t>UK639R</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>MSC BOSTON</t>
-  </si>
-  <si>
-    <t>MC641R</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>641S</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>HYUNDAI SUPREME</t>
-  </si>
-  <si>
-    <t>PN32635E</t>
-  </si>
-  <si>
-    <t>HMM</t>
-  </si>
-  <si>
-    <t>EB1</t>
-  </si>
-  <si>
-    <t>RCC TIANJIN</t>
-  </si>
-  <si>
-    <t>018A</t>
-  </si>
-  <si>
-    <t>Hyundai Glovis</t>
-  </si>
-  <si>
-    <t>BERGAMOT ACE</t>
-  </si>
-  <si>
-    <t>158A</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM BYBLOS</t>
-  </si>
-  <si>
-    <t>CPN00/CPN01</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
     <t>LIBERTY PRIDE</t>
   </si>
   <si>
@@ -311,6 +305,18 @@
     <t>Pacific Terminals</t>
   </si>
   <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>LONG BEACH EXPRESS</t>
+  </si>
+  <si>
+    <t>636N/642S</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
+  </si>
+  <si>
     <t>EB Service 2</t>
   </si>
   <si>
@@ -326,18 +332,6 @@
     <t>Talon Marine Services LLC</t>
   </si>
   <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>LONG BEACH EXPRESS</t>
-  </si>
-  <si>
-    <t>636N/642S</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
-  </si>
-  <si>
     <t>CAPE TAINARO</t>
   </si>
   <si>
@@ -380,9 +374,6 @@
     <t>NORTH STAR</t>
   </si>
   <si>
-    <t>Waiting 4.1 days</t>
-  </si>
-  <si>
     <t>WC4/TP5</t>
   </si>
   <si>
@@ -407,24 +398,24 @@
     <t>269N/269S</t>
   </si>
   <si>
+    <t>THEMISA</t>
+  </si>
+  <si>
+    <t>ED615</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>SALVIA ACE</t>
+  </si>
+  <si>
+    <t>177A</t>
+  </si>
+  <si>
     <t>MODERN LINK</t>
   </si>
   <si>
-    <t>THEMISA</t>
-  </si>
-  <si>
-    <t>ED615</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>SALVIA ACE</t>
-  </si>
-  <si>
-    <t>177A</t>
-  </si>
-  <si>
     <t>SM QINGDAO</t>
   </si>
   <si>
@@ -521,25 +512,25 @@
     <t>159E</t>
   </si>
   <si>
+    <t>CARNATION ACE</t>
+  </si>
+  <si>
+    <t>107A</t>
+  </si>
+  <si>
     <t>POLARIS MILA</t>
   </si>
   <si>
-    <t>CARNATION ACE</t>
-  </si>
-  <si>
-    <t>107A</t>
+    <t>OOCL SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>199E</t>
   </si>
   <si>
     <t>MAUNAWILI</t>
   </si>
   <si>
     <t>642S</t>
-  </si>
-  <si>
-    <t>OOCL SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>199E</t>
   </si>
   <si>
     <t>RJ PFEIFFER</t>
@@ -828,10 +819,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L117" totalsRowShown="0">
-  <autoFilter ref="A1:L117" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L117">
-    <sortCondition ref="J2:J117"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L116" totalsRowShown="0">
+  <autoFilter ref="A1:L116" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L116">
+    <sortCondition ref="J2:J116"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1168,7 +1159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L117"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1470,19 +1461,19 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
       </c>
       <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" t="s">
         <v>44</v>
-      </c>
-      <c r="F9" t="s">
-        <v>23</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
@@ -1494,10 +1485,10 @@
         <v>25</v>
       </c>
       <c r="J9" s="2">
-        <v>46306.541666666664</v>
+        <v>46306.625</v>
       </c>
       <c r="K9" s="2">
-        <v>46306.999305555553</v>
+        <v>46307.166666666664</v>
       </c>
       <c r="L9" t="s">
         <v>26</v>
@@ -1508,57 +1499,51 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
         <v>17</v>
       </c>
-      <c r="H10" t="s">
-        <v>45</v>
-      </c>
       <c r="I10" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J10" s="2">
         <v>46306.625</v>
       </c>
       <c r="K10" s="2">
-        <v>46307.166666666664</v>
+        <v>46308.75</v>
       </c>
       <c r="L10" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
         <v>50</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" t="s">
         <v>52</v>
-      </c>
-      <c r="F11" t="s">
-        <v>23</v>
       </c>
       <c r="G11" t="s">
         <v>17</v>
@@ -1567,10 +1552,10 @@
         <v>18</v>
       </c>
       <c r="J11" s="2">
-        <v>46306.625</v>
+        <v>46307.25</v>
       </c>
       <c r="K11" s="2">
-        <v>46308.75</v>
+        <v>46307.75</v>
       </c>
       <c r="L11" t="s">
         <v>38</v>
@@ -1581,7 +1566,10 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
       </c>
       <c r="D12" t="s">
         <v>53</v>
@@ -1590,7 +1578,7 @@
         <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="G12" t="s">
         <v>17</v>
@@ -1599,10 +1587,10 @@
         <v>18</v>
       </c>
       <c r="J12" s="2">
-        <v>46307.25</v>
+        <v>46308.291666666664</v>
       </c>
       <c r="K12" s="2">
-        <v>46307.75</v>
+        <v>46310.166666666664</v>
       </c>
       <c r="L12" t="s">
         <v>38</v>
@@ -1616,7 +1604,7 @@
         <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
         <v>56</v>
@@ -1637,7 +1625,7 @@
         <v>46308.291666666664</v>
       </c>
       <c r="K13" s="2">
-        <v>46310.166666666664</v>
+        <v>46309.75</v>
       </c>
       <c r="L13" t="s">
         <v>38</v>
@@ -1645,34 +1633,37 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>62</v>
+      </c>
+      <c r="H14" t="s">
+        <v>63</v>
       </c>
       <c r="I14" t="s">
         <v>18</v>
       </c>
       <c r="J14" s="2">
-        <v>46308.291666666664</v>
+        <v>46309.104166666664</v>
       </c>
       <c r="K14" s="2">
-        <v>46309.75</v>
+        <v>46309.916666666664</v>
       </c>
       <c r="L14" t="s">
         <v>38</v>
@@ -1683,34 +1674,31 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
-      </c>
-      <c r="H15" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
         <v>18</v>
       </c>
       <c r="J15" s="2">
-        <v>46309.104166666664</v>
+        <v>46309.208333333336</v>
       </c>
       <c r="K15" s="2">
-        <v>46309.916666666664</v>
+        <v>46310.75</v>
       </c>
       <c r="L15" t="s">
         <v>38</v>
@@ -1721,34 +1709,34 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" t="s">
         <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J16" s="2">
-        <v>46309.208333333336</v>
+        <v>46309.25</v>
       </c>
       <c r="K16" s="2">
-        <v>46310.75</v>
+        <v>46309.708333333336</v>
       </c>
       <c r="L16" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1756,7 +1744,7 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
         <v>21</v>
@@ -1768,7 +1756,7 @@
         <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="G17" t="s">
         <v>17</v>
@@ -1777,10 +1765,10 @@
         <v>25</v>
       </c>
       <c r="J17" s="2">
-        <v>46309.25</v>
+        <v>46309.541666666664</v>
       </c>
       <c r="K17" s="2">
-        <v>46309.708333333336</v>
+        <v>46310.041666666664</v>
       </c>
       <c r="L17" t="s">
         <v>26</v>
@@ -1788,13 +1776,13 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
         <v>75</v>
@@ -1803,54 +1791,57 @@
         <v>76</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s">
         <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J18" s="2">
-        <v>46309.541666666664</v>
+        <v>46309.625</v>
       </c>
       <c r="K18" s="2">
-        <v>46310.041666666664</v>
+        <v>46311.75</v>
       </c>
       <c r="L18" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="E19" s="1">
+        <v>26165</v>
       </c>
       <c r="F19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s">
-        <v>17</v>
+        <v>82</v>
+      </c>
+      <c r="H19" t="s">
+        <v>82</v>
       </c>
       <c r="I19" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="J19" s="2">
         <v>46309.625</v>
       </c>
       <c r="K19" s="2">
-        <v>46311.75</v>
+        <v>46310.041666666664</v>
       </c>
       <c r="L19" t="s">
         <v>38</v>
@@ -1861,37 +1852,34 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" s="1">
-        <v>26165</v>
+        <v>69</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="G20" t="s">
-        <v>85</v>
-      </c>
-      <c r="H20" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="J20" s="2">
-        <v>46309.625</v>
+        <v>46309.75</v>
       </c>
       <c r="K20" s="2">
-        <v>46310.041666666664</v>
+        <v>46310.666666666664</v>
       </c>
       <c r="L20" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1899,31 +1887,34 @@
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
         <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
+      </c>
+      <c r="E21" s="1">
+        <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="G21" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="H21" t="s">
+        <v>87</v>
       </c>
       <c r="I21" t="s">
         <v>25</v>
       </c>
       <c r="J21" s="2">
-        <v>46309.75</v>
+        <v>46310.25</v>
       </c>
       <c r="K21" s="2">
-        <v>46310.666666666664</v>
+        <v>46310.75</v>
       </c>
       <c r="L21" t="s">
         <v>26</v>
@@ -1931,40 +1922,37 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" s="1">
-        <v>4</v>
+        <v>89</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="F22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J22" s="2">
         <v>46310.25</v>
       </c>
       <c r="K22" s="2">
-        <v>46310.75</v>
+        <v>46311.166666666664</v>
       </c>
       <c r="L22" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1975,19 +1963,19 @@
         <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I23" t="s">
         <v>18</v>
@@ -2007,19 +1995,19 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="G24" t="s">
         <v>17</v>
@@ -2028,7 +2016,7 @@
         <v>18</v>
       </c>
       <c r="J24" s="2">
-        <v>46310.25</v>
+        <v>46310.291666666664</v>
       </c>
       <c r="K24" s="2">
         <v>46311.166666666664</v>
@@ -2039,34 +2027,37 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D25" t="s">
         <v>99</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>62</v>
+      </c>
+      <c r="H25" t="s">
+        <v>63</v>
       </c>
       <c r="I25" t="s">
         <v>18</v>
       </c>
       <c r="J25" s="2">
-        <v>46310.291666666664</v>
+        <v>46311.104166666664</v>
       </c>
       <c r="K25" s="2">
-        <v>46311.166666666664</v>
+        <v>46311.916666666664</v>
       </c>
       <c r="L25" t="s">
         <v>38</v>
@@ -2074,37 +2065,37 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
         <v>101</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="G26" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="H26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I26" t="s">
         <v>18</v>
       </c>
       <c r="J26" s="2">
-        <v>46311.104166666664</v>
+        <v>46311.25</v>
       </c>
       <c r="K26" s="2">
-        <v>46311.916666666664</v>
+        <v>46312.166666666664</v>
       </c>
       <c r="L26" t="s">
         <v>38</v>
@@ -2112,37 +2103,34 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F27" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="G27" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="H27" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I27" t="s">
         <v>18</v>
       </c>
       <c r="J27" s="2">
-        <v>46311.25</v>
+        <v>46311.291666666664</v>
       </c>
       <c r="K27" s="2">
-        <v>46312.166666666664</v>
+        <v>46312.125</v>
       </c>
       <c r="L27" t="s">
         <v>38</v>
@@ -2153,34 +2141,37 @@
         <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" t="s">
         <v>106</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" s="1" t="s">
         <v>107</v>
       </c>
       <c r="F28" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="G28" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="J28" s="2">
-        <v>46311.291666666664</v>
+        <v>46311.541666666664</v>
       </c>
       <c r="K28" s="2">
-        <v>46312.125</v>
+        <v>46312.083333333336</v>
       </c>
       <c r="L28" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2188,37 +2179,34 @@
         <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>108</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="E29" s="1">
+        <v>26164</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="J29" s="2">
-        <v>46311.541666666664</v>
+        <v>46311.625</v>
       </c>
       <c r="K29" s="2">
-        <v>46312.083333333336</v>
-      </c>
-      <c r="L29" t="s">
-        <v>26</v>
+        <v>46312.041666666664</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2226,37 +2214,37 @@
         <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
-      </c>
-      <c r="E30" s="1">
-        <v>26164</v>
+        <v>106</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="F30" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="G30" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="I30" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="J30" s="2">
-        <v>46311.625</v>
+        <v>46312.125</v>
       </c>
       <c r="K30" s="2">
-        <v>46312.041666666664</v>
+        <v>46312.666666666664</v>
       </c>
       <c r="L30" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2264,48 +2252,45 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="G31" t="s">
         <v>17</v>
       </c>
-      <c r="H31" t="s">
-        <v>66</v>
-      </c>
       <c r="I31" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="J31" s="2">
-        <v>46312.125</v>
+        <v>46312.5</v>
       </c>
       <c r="K31" s="2">
-        <v>46312.666666666664</v>
+        <v>46315.75</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
         <v>115</v>
@@ -2314,7 +2299,7 @@
         <v>116</v>
       </c>
       <c r="F32" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s">
         <v>17</v>
@@ -2323,10 +2308,10 @@
         <v>18</v>
       </c>
       <c r="J32" s="2">
-        <v>46312.5</v>
+        <v>46312.625</v>
       </c>
       <c r="K32" s="2">
-        <v>46315.75</v>
+        <v>46314.75</v>
       </c>
       <c r="L32" t="s">
         <v>38</v>
@@ -2340,19 +2325,19 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="F33" t="s">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="G33" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I33" t="s">
         <v>18</v>
@@ -2361,7 +2346,7 @@
         <v>46312.625</v>
       </c>
       <c r="K33" s="2">
-        <v>46314.75</v>
+        <v>46313.75</v>
       </c>
       <c r="L33" t="s">
         <v>38</v>
@@ -2369,37 +2354,37 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="F34" t="s">
         <v>121</v>
       </c>
-      <c r="F34" t="s">
-        <v>36</v>
-      </c>
       <c r="G34" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J34" s="2">
-        <v>46312.625</v>
+        <v>46314.25</v>
       </c>
       <c r="K34" s="2">
-        <v>46313.75</v>
+        <v>46314.75</v>
       </c>
       <c r="L34" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2407,7 +2392,7 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
         <v>21</v>
@@ -2415,11 +2400,11 @@
       <c r="D35" t="s">
         <v>122</v>
       </c>
-      <c r="E35" s="1">
-        <v>2</v>
+      <c r="E35" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="F35" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="G35" t="s">
         <v>17</v>
@@ -2442,19 +2427,19 @@
         <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
         <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" s="1" t="s">
         <v>124</v>
       </c>
+      <c r="E36" s="1">
+        <v>2</v>
+      </c>
       <c r="F36" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="G36" t="s">
         <v>17</v>
@@ -2474,61 +2459,61 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="F37" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="G37" t="s">
         <v>17</v>
       </c>
+      <c r="H37" t="s">
+        <v>63</v>
+      </c>
       <c r="I37" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J37" s="2">
-        <v>46314.25</v>
+        <v>46314.625</v>
       </c>
       <c r="K37" s="2">
-        <v>46314.75</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L37" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
+        <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>54</v>
+        <v>126</v>
+      </c>
+      <c r="E38" s="1">
+        <v>34</v>
       </c>
       <c r="F38" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="G38" t="s">
         <v>17</v>
       </c>
-      <c r="H38" t="s">
-        <v>66</v>
-      </c>
       <c r="I38" t="s">
         <v>18</v>
       </c>
@@ -2536,7 +2521,7 @@
         <v>46314.625</v>
       </c>
       <c r="K38" s="2">
-        <v>46315.166666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L38" t="s">
         <v>38</v>
@@ -2547,31 +2532,31 @@
         <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s">
         <v>129</v>
       </c>
-      <c r="E39" s="1">
-        <v>34</v>
+      <c r="E39" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="G39" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="I39" t="s">
         <v>18</v>
       </c>
       <c r="J39" s="2">
-        <v>46314.625</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K39" s="2">
-        <v>46318.75</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="L39" t="s">
         <v>38</v>
@@ -2582,31 +2567,31 @@
         <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>131</v>
+        <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F40" t="s">
-        <v>134</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="I40" t="s">
         <v>18</v>
       </c>
       <c r="J40" s="2">
-        <v>46315.208333333336</v>
+        <v>46315.25</v>
       </c>
       <c r="K40" s="2">
-        <v>46316.791666666664</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L40" t="s">
         <v>38</v>
@@ -2614,31 +2599,31 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D41" t="s">
+        <v>135</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G41" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s">
         <v>18</v>
       </c>
       <c r="J41" s="2">
-        <v>46315.25</v>
+        <v>46315.291666666664</v>
       </c>
       <c r="K41" s="2">
         <v>46317.166666666664</v>
@@ -2658,10 +2643,10 @@
         <v>39</v>
       </c>
       <c r="D42" t="s">
+        <v>137</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="F42" t="s">
         <v>31</v>
@@ -2673,10 +2658,10 @@
         <v>18</v>
       </c>
       <c r="J42" s="2">
-        <v>46315.291666666664</v>
+        <v>46315.708333333336</v>
       </c>
       <c r="K42" s="2">
-        <v>46317.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L42" t="s">
         <v>38</v>
@@ -2684,37 +2669,40 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D43" t="s">
+        <v>139</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="F43" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>62</v>
+      </c>
+      <c r="H43" t="s">
+        <v>63</v>
       </c>
       <c r="I43" t="s">
         <v>18</v>
       </c>
       <c r="J43" s="2">
-        <v>46315.708333333336</v>
+        <v>46316.104166666664</v>
       </c>
       <c r="K43" s="2">
-        <v>46317.75</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L43" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2722,34 +2710,34 @@
         <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
+        <v>141</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="F44" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="G44" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H44" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="I44" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J44" s="2">
-        <v>46316.104166666664</v>
+        <v>46316.25</v>
       </c>
       <c r="K44" s="2">
-        <v>46316.916666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L44" t="s">
         <v>26</v>
@@ -2760,25 +2748,22 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C45" t="s">
         <v>21</v>
       </c>
       <c r="D45" t="s">
-        <v>144</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
+      </c>
+      <c r="E45" s="1">
+        <v>63</v>
       </c>
       <c r="F45" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="G45" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="I45" t="s">
         <v>25</v>
@@ -2798,34 +2783,34 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
-      </c>
-      <c r="E46" s="1">
-        <v>63</v>
+        <v>144</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="F46" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="G46" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I46" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J46" s="2">
-        <v>46316.25</v>
+        <v>46316.625</v>
       </c>
       <c r="K46" s="2">
-        <v>46316.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L46" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2833,34 +2818,31 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="D47" t="s">
-        <v>83</v>
-      </c>
-      <c r="E47" s="1">
-        <v>26169</v>
+        <v>144</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="F47" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G47" t="s">
-        <v>85</v>
-      </c>
-      <c r="H47" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J47" s="2">
         <v>46316.625</v>
       </c>
       <c r="K47" s="2">
-        <v>46317.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L47" t="s">
         <v>38</v>
@@ -2871,31 +2853,34 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="C48" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="D48" t="s">
-        <v>147</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>148</v>
+        <v>80</v>
+      </c>
+      <c r="E48" s="1">
+        <v>26169</v>
       </c>
       <c r="F48" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s">
-        <v>17</v>
+        <v>82</v>
+      </c>
+      <c r="H48" t="s">
+        <v>82</v>
       </c>
       <c r="I48" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="J48" s="2">
         <v>46316.625</v>
       </c>
       <c r="K48" s="2">
-        <v>46319.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L48" t="s">
         <v>38</v>
@@ -2906,34 +2891,37 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="C49" t="s">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="D49" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F49" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="G49" t="s">
         <v>17</v>
       </c>
+      <c r="H49" t="s">
+        <v>45</v>
+      </c>
       <c r="I49" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J49" s="2">
-        <v>46316.625</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="K49" s="2">
-        <v>46319.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L49" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2941,45 +2929,42 @@
         <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>42</v>
-      </c>
-      <c r="C50" t="s">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="D50" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F50" t="s">
+        <v>131</v>
+      </c>
+      <c r="G50" t="s">
         <v>149</v>
       </c>
-      <c r="F50" t="s">
-        <v>125</v>
-      </c>
-      <c r="G50" t="s">
-        <v>17</v>
-      </c>
-      <c r="H50" t="s">
-        <v>45</v>
-      </c>
       <c r="I50" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J50" s="2">
-        <v>46316.791666666664</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K50" s="2">
-        <v>46317.75</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L50" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>130</v>
+        <v>32</v>
+      </c>
+      <c r="C51" t="s">
+        <v>33</v>
       </c>
       <c r="D51" t="s">
         <v>150</v>
@@ -2988,19 +2973,19 @@
         <v>151</v>
       </c>
       <c r="F51" t="s">
-        <v>134</v>
+        <v>36</v>
       </c>
       <c r="G51" t="s">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="I51" t="s">
         <v>18</v>
       </c>
       <c r="J51" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.25</v>
       </c>
       <c r="K51" s="2">
-        <v>46318.708333333336</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L51" t="s">
         <v>38</v>
@@ -3011,28 +2996,25 @@
         <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D52" t="s">
+        <v>152</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="F52" t="s">
-        <v>36</v>
-      </c>
-      <c r="G52" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I52" t="s">
         <v>18</v>
       </c>
       <c r="J52" s="2">
-        <v>46317.25</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K52" s="2">
         <v>46318.166666666664</v>
@@ -3046,10 +3028,10 @@
         <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C53" t="s">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="D53" t="s">
         <v>155</v>
@@ -3058,16 +3040,16 @@
         <v>156</v>
       </c>
       <c r="F53" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="I53" t="s">
         <v>18</v>
       </c>
       <c r="J53" s="2">
-        <v>46317.291666666664</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K53" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L53" t="s">
         <v>38</v>
@@ -3075,34 +3057,37 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C54" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" t="s">
         <v>157</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="F54" t="s">
-        <v>93</v>
+        <v>23</v>
+      </c>
+      <c r="G54" t="s">
+        <v>17</v>
       </c>
       <c r="I54" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J54" s="2">
-        <v>46317.927777777775</v>
+        <v>46318.25</v>
       </c>
       <c r="K54" s="2">
-        <v>46318.969444444447</v>
+        <v>46318.75</v>
       </c>
       <c r="L54" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3110,19 +3095,19 @@
         <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C55" t="s">
         <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E55" s="1">
         <v>4</v>
       </c>
       <c r="F55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G55" t="s">
         <v>17</v>
@@ -3142,63 +3127,54 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="D56" t="s">
+        <v>160</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="F56" t="s">
-        <v>23</v>
-      </c>
-      <c r="G56" t="s">
-        <v>17</v>
+        <v>103</v>
       </c>
       <c r="I56" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J56" s="2">
-        <v>46318.25</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K56" s="2">
-        <v>46318.75</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="L56" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D57" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F57" t="s">
-        <v>65</v>
-      </c>
-      <c r="G57" t="s">
-        <v>65</v>
-      </c>
-      <c r="H57" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="I57" t="s">
         <v>18</v>
@@ -3207,30 +3183,36 @@
         <v>46318.291666666664</v>
       </c>
       <c r="K57" s="2">
-        <v>46319.125</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="L57" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C58" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F58" t="s">
-        <v>105</v>
+        <v>62</v>
+      </c>
+      <c r="G58" t="s">
+        <v>62</v>
+      </c>
+      <c r="H58" t="s">
+        <v>63</v>
       </c>
       <c r="I58" t="s">
         <v>18</v>
@@ -3239,42 +3221,45 @@
         <v>46318.291666666664</v>
       </c>
       <c r="K58" s="2">
-        <v>46319.666666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L58" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D59" t="s">
-        <v>165</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>166</v>
+        <v>110</v>
+      </c>
+      <c r="E59" s="1">
+        <v>26168</v>
       </c>
       <c r="F59" t="s">
-        <v>105</v>
+        <v>81</v>
+      </c>
+      <c r="G59" t="s">
+        <v>82</v>
+      </c>
+      <c r="H59" t="s">
+        <v>82</v>
       </c>
       <c r="I59" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="J59" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.625</v>
       </c>
       <c r="K59" s="2">
-        <v>46319.666666666664</v>
-      </c>
-      <c r="L59" t="s">
-        <v>38</v>
+        <v>46319.041666666664</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3282,37 +3267,31 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="D60" t="s">
-        <v>112</v>
-      </c>
-      <c r="E60" s="1">
-        <v>26168</v>
+        <v>164</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="F60" t="s">
-        <v>84</v>
-      </c>
-      <c r="G60" t="s">
-        <v>85</v>
-      </c>
-      <c r="H60" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="I60" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J60" s="2">
-        <v>46318.625</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K60" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L60" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3320,31 +3299,34 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F61" t="s">
-        <v>65</v>
+        <v>121</v>
+      </c>
+      <c r="G61" t="s">
+        <v>17</v>
       </c>
       <c r="I61" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J61" s="2">
-        <v>46318.704861111109</v>
+        <v>46319.25</v>
       </c>
       <c r="K61" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.75</v>
       </c>
       <c r="L61" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3352,19 +3334,19 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="C62" t="s">
         <v>21</v>
       </c>
       <c r="D62" t="s">
+        <v>167</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
         <v>168</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="F62" t="s">
-        <v>125</v>
       </c>
       <c r="G62" t="s">
         <v>17</v>
@@ -3376,7 +3358,7 @@
         <v>46319.25</v>
       </c>
       <c r="K62" s="2">
-        <v>46319.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L62" t="s">
         <v>26</v>
@@ -3387,63 +3369,60 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="C63" t="s">
-        <v>21</v>
+        <v>128</v>
       </c>
       <c r="D63" t="s">
+        <v>169</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E63" s="1">
-        <v>1</v>
-      </c>
       <c r="F63" t="s">
-        <v>171</v>
-      </c>
-      <c r="G63" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="I63" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J63" s="2">
-        <v>46319.25</v>
+        <v>46320</v>
       </c>
       <c r="K63" s="2">
-        <v>46322.75</v>
+        <v>46322</v>
       </c>
       <c r="L63" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B64" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="C64" t="s">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="D64" t="s">
+        <v>171</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="F64" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="I64" t="s">
         <v>18</v>
       </c>
       <c r="J64" s="2">
-        <v>46320</v>
+        <v>46320.21875</v>
       </c>
       <c r="K64" s="2">
-        <v>46322</v>
+        <v>46324.59375</v>
       </c>
       <c r="L64" t="s">
         <v>38</v>
@@ -3454,28 +3433,28 @@
         <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C65" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="D65" t="s">
+        <v>173</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="F65" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="I65" t="s">
         <v>18</v>
       </c>
       <c r="J65" s="2">
-        <v>46320.21875</v>
+        <v>46320.649305555555</v>
       </c>
       <c r="K65" s="2">
-        <v>46324.59375</v>
+        <v>46321.149305555555</v>
       </c>
       <c r="L65" t="s">
         <v>38</v>
@@ -3483,31 +3462,34 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C66" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="D66" t="s">
+        <v>175</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="F66" t="s">
-        <v>31</v>
+        <v>16</v>
+      </c>
+      <c r="G66" t="s">
+        <v>24</v>
       </c>
       <c r="I66" t="s">
         <v>18</v>
       </c>
       <c r="J66" s="2">
-        <v>46320.649305555555</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K66" s="2">
-        <v>46321.149305555555</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L66" t="s">
         <v>38</v>
@@ -3518,16 +3500,16 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C67" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D67" t="s">
+        <v>177</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="F67" t="s">
         <v>16</v>
@@ -3539,7 +3521,7 @@
         <v>18</v>
       </c>
       <c r="J67" s="2">
-        <v>46321.208333333336</v>
+        <v>46321.25</v>
       </c>
       <c r="K67" s="2">
         <v>46323.166666666664</v>
@@ -3553,31 +3535,31 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>180</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
+      </c>
+      <c r="E68" s="1">
+        <v>21</v>
       </c>
       <c r="F68" t="s">
         <v>16</v>
       </c>
       <c r="G68" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I68" t="s">
         <v>18</v>
       </c>
       <c r="J68" s="2">
-        <v>46321.25</v>
+        <v>46321.625</v>
       </c>
       <c r="K68" s="2">
-        <v>46323.166666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L68" t="s">
         <v>38</v>
@@ -3588,92 +3570,89 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D69" t="s">
-        <v>182</v>
-      </c>
-      <c r="E69" s="1">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="F69" t="s">
-        <v>16</v>
+        <v>86</v>
       </c>
       <c r="G69" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="H69" t="s">
+        <v>87</v>
       </c>
       <c r="I69" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J69" s="2">
-        <v>46321.625</v>
+        <v>46322.25</v>
       </c>
       <c r="K69" s="2">
-        <v>46325.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L69" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>42</v>
-      </c>
-      <c r="C70" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D70" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F70" t="s">
-        <v>88</v>
-      </c>
-      <c r="G70" t="s">
-        <v>24</v>
-      </c>
-      <c r="H70" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="I70" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J70" s="2">
-        <v>46322.25</v>
+        <v>46322.256249999999</v>
       </c>
       <c r="K70" s="2">
-        <v>46322.75</v>
+        <v>46323.381249999999</v>
       </c>
       <c r="L70" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>127</v>
+      </c>
+      <c r="C71" t="s">
+        <v>128</v>
       </c>
       <c r="D71" t="s">
-        <v>184</v>
+        <v>182</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="F71" t="s">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="I71" t="s">
         <v>18</v>
       </c>
       <c r="J71" s="2">
-        <v>46322.256249999999</v>
+        <v>46322.388194444444</v>
       </c>
       <c r="K71" s="2">
-        <v>46323.381249999999</v>
+        <v>46325.388194444444</v>
       </c>
       <c r="L71" t="s">
         <v>38</v>
@@ -3684,31 +3663,34 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>130</v>
+        <v>68</v>
       </c>
       <c r="C72" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
+        <v>184</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="F72" t="s">
-        <v>134</v>
+        <v>23</v>
+      </c>
+      <c r="G72" t="s">
+        <v>17</v>
       </c>
       <c r="I72" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J72" s="2">
-        <v>46322.388194444444</v>
+        <v>46323.25</v>
       </c>
       <c r="K72" s="2">
-        <v>46325.388194444444</v>
+        <v>46323.75</v>
       </c>
       <c r="L72" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3716,34 +3698,28 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="D73" t="s">
-        <v>187</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="F73" t="s">
-        <v>23</v>
-      </c>
-      <c r="G73" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="I73" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J73" s="2">
-        <v>46323.25</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K73" s="2">
-        <v>46323.75</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L73" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3751,25 +3727,28 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="D74" t="s">
-        <v>101</v>
+        <v>186</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="F74" t="s">
-        <v>65</v>
+        <v>188</v>
       </c>
       <c r="I74" t="s">
         <v>18</v>
       </c>
       <c r="J74" s="2">
-        <v>46323.291666666664</v>
+        <v>46323.622916666667</v>
       </c>
       <c r="K74" s="2">
-        <v>46323.791666666664</v>
+        <v>46324.875</v>
       </c>
       <c r="L74" t="s">
         <v>38</v>
@@ -3780,28 +3759,34 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="C75" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="D75" t="s">
-        <v>189</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>190</v>
+        <v>80</v>
+      </c>
+      <c r="E75" s="1">
+        <v>26173</v>
       </c>
       <c r="F75" t="s">
-        <v>191</v>
+        <v>81</v>
+      </c>
+      <c r="G75" t="s">
+        <v>82</v>
+      </c>
+      <c r="H75" t="s">
+        <v>82</v>
       </c>
       <c r="I75" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="J75" s="2">
-        <v>46323.622916666667</v>
+        <v>46323.625</v>
       </c>
       <c r="K75" s="2">
-        <v>46324.875</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L75" t="s">
         <v>38</v>
@@ -3812,34 +3797,28 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>83</v>
-      </c>
-      <c r="E76" s="1">
-        <v>26173</v>
+        <v>189</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="F76" t="s">
-        <v>84</v>
-      </c>
-      <c r="G76" t="s">
-        <v>85</v>
-      </c>
-      <c r="H76" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="I76" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J76" s="2">
         <v>46323.625</v>
       </c>
       <c r="K76" s="2">
-        <v>46324.041666666664</v>
+        <v>46327.541666666664</v>
       </c>
       <c r="L76" t="s">
         <v>38</v>
@@ -3856,10 +3835,10 @@
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F77" t="s">
         <v>23</v>
@@ -3882,16 +3861,16 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="D78" t="s">
+        <v>191</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="F78" t="s">
         <v>23</v>
@@ -3900,10 +3879,10 @@
         <v>18</v>
       </c>
       <c r="J78" s="2">
-        <v>46323.625</v>
+        <v>46323.661111111112</v>
       </c>
       <c r="K78" s="2">
-        <v>46327.541666666664</v>
+        <v>46327.202777777777</v>
       </c>
       <c r="L78" t="s">
         <v>38</v>
@@ -3914,16 +3893,16 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C79" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D79" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F79" t="s">
         <v>23</v>
@@ -3946,31 +3925,34 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D80" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F80" t="s">
         <v>23</v>
       </c>
+      <c r="G80" t="s">
+        <v>17</v>
+      </c>
       <c r="I80" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J80" s="2">
-        <v>46323.661111111112</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K80" s="2">
-        <v>46327.202777777777</v>
+        <v>46324.75</v>
       </c>
       <c r="L80" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3978,60 +3960,57 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>42</v>
-      </c>
-      <c r="C81" t="s">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="D81" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F81" t="s">
-        <v>23</v>
-      </c>
-      <c r="G81" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="I81" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J81" s="2">
-        <v>46323.791666666664</v>
+        <v>46324</v>
       </c>
       <c r="K81" s="2">
-        <v>46324.75</v>
+        <v>46326</v>
       </c>
       <c r="L81" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>130</v>
+        <v>28</v>
+      </c>
+      <c r="C82" t="s">
+        <v>55</v>
       </c>
       <c r="D82" t="s">
+        <v>195</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="F82" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="I82" t="s">
         <v>18</v>
       </c>
       <c r="J82" s="2">
-        <v>46324</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K82" s="2">
-        <v>46326</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L82" t="s">
         <v>38</v>
@@ -4042,28 +4021,28 @@
         <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C83" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="D83" t="s">
+        <v>197</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="F83" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="I83" t="s">
         <v>18</v>
       </c>
       <c r="J83" s="2">
-        <v>46325.003472222219</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K83" s="2">
-        <v>46325.878472222219</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L83" t="s">
         <v>38</v>
@@ -4071,34 +4050,37 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C84" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="D84" t="s">
+        <v>199</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="F84" t="s">
-        <v>93</v>
+        <v>23</v>
+      </c>
+      <c r="G84" t="s">
+        <v>17</v>
       </c>
       <c r="I84" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J84" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.25</v>
       </c>
       <c r="K84" s="2">
-        <v>46326.098611111112</v>
+        <v>46325.75</v>
       </c>
       <c r="L84" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4106,31 +4088,25 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C85" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="D85" t="s">
-        <v>202</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>203</v>
+        <v>139</v>
       </c>
       <c r="F85" t="s">
-        <v>23</v>
-      </c>
-      <c r="G85" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="I85" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J85" s="2">
-        <v>46325.25</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K85" s="2">
-        <v>46325.75</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L85" t="s">
         <v>26</v>
@@ -4141,28 +4117,34 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C86" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="D86" t="s">
-        <v>142</v>
+        <v>110</v>
+      </c>
+      <c r="E86" s="1">
+        <v>26172</v>
       </c>
       <c r="F86" t="s">
-        <v>65</v>
+        <v>81</v>
+      </c>
+      <c r="G86" t="s">
+        <v>82</v>
+      </c>
+      <c r="H86" t="s">
+        <v>82</v>
       </c>
       <c r="I86" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="J86" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.625</v>
       </c>
       <c r="K86" s="2">
-        <v>46325.833333333336</v>
-      </c>
-      <c r="L86" t="s">
-        <v>26</v>
+        <v>46326.041666666664</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4170,104 +4152,101 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="D87" t="s">
-        <v>112</v>
-      </c>
-      <c r="E87" s="1">
-        <v>26172</v>
+        <v>199</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="F87" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="G87" t="s">
-        <v>85</v>
-      </c>
-      <c r="H87" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="I87" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="J87" s="2">
-        <v>46325.625</v>
+        <v>46325.791666666664</v>
       </c>
       <c r="K87" s="2">
-        <v>46326.041666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L87" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C88" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D88" t="s">
+        <v>201</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="F88" t="s">
-        <v>23</v>
-      </c>
-      <c r="G88" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I88" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J88" s="2">
-        <v>46325.791666666664</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K88" s="2">
-        <v>46326.75</v>
+        <v>46328.125</v>
       </c>
       <c r="L88" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D89" t="s">
+        <v>203</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="F89" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="G89" t="s">
+        <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J89" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K89" s="2">
-        <v>46328.125</v>
+        <v>46326.75</v>
       </c>
       <c r="L89" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4275,34 +4254,28 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C90" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="D90" t="s">
-        <v>206</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="F90" t="s">
-        <v>23</v>
-      </c>
-      <c r="G90" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="I90" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J90" s="2">
-        <v>46326.25</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K90" s="2">
         <v>46326.75</v>
       </c>
       <c r="L90" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4310,25 +4283,28 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C91" t="s">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="D91" t="s">
-        <v>107</v>
+        <v>205</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="F91" t="s">
-        <v>65</v>
+        <v>188</v>
       </c>
       <c r="I91" t="s">
         <v>18</v>
       </c>
       <c r="J91" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K91" s="2">
-        <v>46326.75</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L91" t="s">
         <v>38</v>
@@ -4336,31 +4312,31 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C92" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D92" t="s">
+        <v>207</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="F92" t="s">
-        <v>191</v>
+        <v>77</v>
       </c>
       <c r="I92" t="s">
         <v>18</v>
       </c>
       <c r="J92" s="2">
-        <v>46326.833333333336</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K92" s="2">
-        <v>46329.583333333336</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L92" t="s">
         <v>38</v>
@@ -4368,95 +4344,98 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C93" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="D93" t="s">
+        <v>209</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="F93" t="s">
-        <v>80</v>
+        <v>121</v>
+      </c>
+      <c r="G93" t="s">
+        <v>17</v>
       </c>
       <c r="I93" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J93" s="2">
-        <v>46327.166666666664</v>
+        <v>46327.25</v>
       </c>
       <c r="K93" s="2">
-        <v>46328.541666666664</v>
+        <v>46327.75</v>
       </c>
       <c r="L93" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>71</v>
-      </c>
-      <c r="C94" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D94" t="s">
-        <v>212</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F94" t="s">
-        <v>125</v>
-      </c>
-      <c r="G94" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I94" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J94" s="2">
-        <v>46327.25</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K94" s="2">
-        <v>46327.75</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L94" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>32</v>
+        <v>84</v>
+      </c>
+      <c r="C95" t="s">
+        <v>21</v>
       </c>
       <c r="D95" t="s">
-        <v>214</v>
+        <v>209</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="F95" t="s">
-        <v>55</v>
+        <v>121</v>
+      </c>
+      <c r="G95" t="s">
+        <v>17</v>
       </c>
       <c r="I95" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J95" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.791666666664</v>
       </c>
       <c r="K95" s="2">
-        <v>46328.833333333336</v>
+        <v>46328.75</v>
       </c>
       <c r="L95" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4464,10 +4443,10 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D96" t="s">
         <v>212</v>
@@ -4476,22 +4455,19 @@
         <v>213</v>
       </c>
       <c r="F96" t="s">
-        <v>125</v>
-      </c>
-      <c r="G96" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I96" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J96" s="2">
-        <v>46327.791666666664</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K96" s="2">
-        <v>46328.75</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L96" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4499,28 +4475,28 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="D97" t="s">
+        <v>214</v>
+      </c>
+      <c r="E97" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>216</v>
-      </c>
       <c r="F97" t="s">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="I97" t="s">
         <v>18</v>
       </c>
       <c r="J97" s="2">
-        <v>46327.904861111114</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K97" s="2">
-        <v>46331.196527777778</v>
+        <v>46332.625</v>
       </c>
       <c r="L97" t="s">
         <v>38</v>
@@ -4528,31 +4504,25 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
-      </c>
-      <c r="C98" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="D98" t="s">
-        <v>217</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F98" t="s">
-        <v>191</v>
+        <v>52</v>
       </c>
       <c r="I98" t="s">
         <v>18</v>
       </c>
       <c r="J98" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.083333333336</v>
       </c>
       <c r="K98" s="2">
-        <v>46332.625</v>
+        <v>46331.208333333336</v>
       </c>
       <c r="L98" t="s">
         <v>38</v>
@@ -4560,25 +4530,31 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>32</v>
+        <v>127</v>
+      </c>
+      <c r="C99" t="s">
+        <v>128</v>
       </c>
       <c r="D99" t="s">
-        <v>219</v>
+        <v>217</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="F99" t="s">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="I99" t="s">
         <v>18</v>
       </c>
       <c r="J99" s="2">
-        <v>46330.083333333336</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K99" s="2">
-        <v>46331.208333333336</v>
+        <v>46333.208333333336</v>
       </c>
       <c r="L99" t="s">
         <v>38</v>
@@ -4589,28 +4565,25 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="C100" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="D100" t="s">
-        <v>220</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>221</v>
+        <v>80</v>
       </c>
       <c r="F100" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="I100" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="J100" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.625</v>
       </c>
       <c r="K100" s="2">
-        <v>46333.208333333336</v>
+        <v>46331.125</v>
       </c>
       <c r="L100" t="s">
         <v>38</v>
@@ -4621,25 +4594,28 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="C101" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="D101" t="s">
-        <v>83</v>
+        <v>219</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="F101" t="s">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="I101" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="J101" s="2">
-        <v>46330.625</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K101" s="2">
-        <v>46331.125</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L101" t="s">
         <v>38</v>
@@ -4653,16 +4629,16 @@
         <v>13</v>
       </c>
       <c r="C102" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D102" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F102" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I102" t="s">
         <v>18</v>
@@ -4682,28 +4658,25 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="C103" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="D103" t="s">
-        <v>222</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>223</v>
+        <v>164</v>
       </c>
       <c r="F103" t="s">
-        <v>191</v>
+        <v>62</v>
       </c>
       <c r="I103" t="s">
         <v>18</v>
       </c>
       <c r="J103" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K103" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L103" t="s">
         <v>38</v>
@@ -4711,28 +4684,31 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B104" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="C104" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="D104" t="s">
-        <v>167</v>
+        <v>221</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="F104" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="I104" t="s">
         <v>18</v>
       </c>
       <c r="J104" s="2">
-        <v>46330.704861111109</v>
+        <v>46330.75</v>
       </c>
       <c r="K104" s="2">
-        <v>46331.204861111109</v>
+        <v>46332.75</v>
       </c>
       <c r="L104" t="s">
         <v>38</v>
@@ -4743,28 +4719,28 @@
         <v>27</v>
       </c>
       <c r="B105" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C105" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D105" t="s">
+        <v>223</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="F105" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="I105" t="s">
         <v>18</v>
       </c>
       <c r="J105" s="2">
-        <v>46330.75</v>
+        <v>46331.020833333336</v>
       </c>
       <c r="K105" s="2">
-        <v>46332.75</v>
+        <v>46332.520833333336</v>
       </c>
       <c r="L105" t="s">
         <v>38</v>
@@ -4775,28 +4751,25 @@
         <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C106" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="D106" t="s">
-        <v>226</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F106" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="I106" t="s">
         <v>18</v>
       </c>
       <c r="J106" s="2">
-        <v>46331.020833333336</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K106" s="2">
-        <v>46332.520833333336</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L106" t="s">
         <v>38</v>
@@ -4804,28 +4777,31 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C107" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D107" t="s">
-        <v>228</v>
+        <v>226</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="F107" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="I107" t="s">
         <v>18</v>
       </c>
       <c r="J107" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K107" s="2">
-        <v>46332.166666666664</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L107" t="s">
         <v>38</v>
@@ -4836,19 +4812,19 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C108" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D108" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F108" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I108" t="s">
         <v>18</v>
@@ -4865,31 +4841,31 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B109" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C109" t="s">
-        <v>50</v>
+        <v>154</v>
       </c>
       <c r="D109" t="s">
+        <v>228</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="F109" t="s">
-        <v>191</v>
+        <v>95</v>
       </c>
       <c r="I109" t="s">
         <v>18</v>
       </c>
       <c r="J109" s="2">
-        <v>46331.496527777781</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K109" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L109" t="s">
         <v>38</v>
@@ -4903,25 +4879,25 @@
         <v>32</v>
       </c>
       <c r="C110" t="s">
-        <v>157</v>
+        <v>33</v>
       </c>
       <c r="D110" t="s">
+        <v>230</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="F110" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="I110" t="s">
         <v>18</v>
       </c>
       <c r="J110" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.083333333336</v>
       </c>
       <c r="K110" s="2">
-        <v>46332.597916666666</v>
+        <v>46333.291666666664</v>
       </c>
       <c r="L110" t="s">
         <v>38</v>
@@ -4929,34 +4905,37 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="C111" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D111" t="s">
-        <v>233</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
+      </c>
+      <c r="E111" s="1">
+        <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>36</v>
+        <v>71</v>
+      </c>
+      <c r="G111" t="s">
+        <v>17</v>
       </c>
       <c r="I111" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J111" s="2">
-        <v>46332.083333333336</v>
+        <v>46332.25</v>
       </c>
       <c r="K111" s="2">
-        <v>46333.291666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L111" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -4964,19 +4943,19 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C112" t="s">
         <v>21</v>
       </c>
       <c r="D112" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E112" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F112" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G112" t="s">
         <v>17</v>
@@ -4999,34 +4978,31 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D113" t="s">
-        <v>236</v>
-      </c>
-      <c r="E113" s="1">
-        <v>10</v>
+        <v>234</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="F113" t="s">
-        <v>74</v>
-      </c>
-      <c r="G113" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I113" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J113" s="2">
         <v>46332.25</v>
       </c>
       <c r="K113" s="2">
-        <v>46332.75</v>
+        <v>46336.041666666664</v>
       </c>
       <c r="L113" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -5040,10 +5016,10 @@
         <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F114" t="s">
         <v>23</v>
@@ -5066,28 +5042,25 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="C115" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="D115" t="s">
-        <v>237</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>238</v>
+        <v>99</v>
       </c>
       <c r="F115" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="I115" t="s">
         <v>18</v>
       </c>
       <c r="J115" s="2">
-        <v>46332.25</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K115" s="2">
-        <v>46336.041666666664</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L115" t="s">
         <v>38</v>
@@ -5098,57 +5071,25 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C116" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="D116" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F116" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="I116" t="s">
         <v>18</v>
       </c>
       <c r="J116" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K116" s="2">
-        <v>46332.791666666664</v>
-      </c>
-      <c r="L116" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12">
-      <c r="A117" t="s">
-        <v>12</v>
-      </c>
-      <c r="B117" t="s">
-        <v>81</v>
-      </c>
-      <c r="C117" t="s">
-        <v>111</v>
-      </c>
-      <c r="D117" t="s">
-        <v>112</v>
-      </c>
-      <c r="F117" t="s">
-        <v>84</v>
-      </c>
-      <c r="I117" t="s">
-        <v>18</v>
-      </c>
-      <c r="J117" s="2">
-        <v>46332.541666666664</v>
-      </c>
-      <c r="K117" s="2">
         <v>46333.041666666664</v>
-      </c>
-      <c r="L117" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -5160,15 +5101,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -5176,13 +5108,13 @@
 </scriptIds>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5320,18 +5252,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>